--- a/data/file_generation/input/data_358/ASD数据汇总表.xlsx
+++ b/data/file_generation/input/data_358/ASD数据汇总表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tianjiaojiao/Desktop/田姣姣/input/data_358/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE130FCB-4357-704E-B59C-F7FCFDB88F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9854BFCF-2A80-DE4D-AF52-F0DB18E975B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="760" windowWidth="29000" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33020" yWindow="3040" windowWidth="29000" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,588 +95,6 @@
     <t>沟通</t>
   </si>
   <si>
-    <t>陈超</t>
-  </si>
-  <si>
-    <t>陈芳</t>
-  </si>
-  <si>
-    <t>陈桂英</t>
-  </si>
-  <si>
-    <t>陈建华</t>
-  </si>
-  <si>
-    <t>陈军</t>
-  </si>
-  <si>
-    <t>陈磊</t>
-  </si>
-  <si>
-    <t>陈娜</t>
-  </si>
-  <si>
-    <t>陈秀英</t>
-  </si>
-  <si>
-    <t>陈艳</t>
-  </si>
-  <si>
-    <t>陈洋</t>
-  </si>
-  <si>
-    <t>陈志强</t>
-  </si>
-  <si>
-    <t>高桂英</t>
-  </si>
-  <si>
-    <t>高建华</t>
-  </si>
-  <si>
-    <t>高静</t>
-  </si>
-  <si>
-    <t>高军</t>
-  </si>
-  <si>
-    <t>高磊</t>
-  </si>
-  <si>
-    <t>高强</t>
-  </si>
-  <si>
-    <t>高勇</t>
-  </si>
-  <si>
-    <t>高志强</t>
-  </si>
-  <si>
-    <t>郭超</t>
-  </si>
-  <si>
-    <t>郭桂英</t>
-  </si>
-  <si>
-    <t>郭建华</t>
-  </si>
-  <si>
-    <t>郭杰</t>
-  </si>
-  <si>
-    <t>郭静</t>
-  </si>
-  <si>
-    <t>郭丽</t>
-  </si>
-  <si>
-    <t>郭娜</t>
-  </si>
-  <si>
-    <t>郭强</t>
-  </si>
-  <si>
-    <t>郭涛</t>
-  </si>
-  <si>
-    <t>郭艳</t>
-  </si>
-  <si>
-    <t>郭洋</t>
-  </si>
-  <si>
-    <t>何超</t>
-  </si>
-  <si>
-    <t>何芳</t>
-  </si>
-  <si>
-    <t>何静</t>
-  </si>
-  <si>
-    <t>何军</t>
-  </si>
-  <si>
-    <t>何丽</t>
-  </si>
-  <si>
-    <t>何敏</t>
-  </si>
-  <si>
-    <t>何涛</t>
-  </si>
-  <si>
-    <t>何勇</t>
-  </si>
-  <si>
-    <t>黄超</t>
-  </si>
-  <si>
-    <t>黄杰</t>
-  </si>
-  <si>
-    <t>黄磊</t>
-  </si>
-  <si>
-    <t>黄丽</t>
-  </si>
-  <si>
-    <t>黄敏</t>
-  </si>
-  <si>
-    <t>黄明</t>
-  </si>
-  <si>
-    <t>黄强</t>
-  </si>
-  <si>
-    <t>黄伟</t>
-  </si>
-  <si>
-    <t>黄秀英</t>
-  </si>
-  <si>
-    <t>黄洋</t>
-  </si>
-  <si>
-    <t>胡超</t>
-  </si>
-  <si>
-    <t>胡桂英</t>
-  </si>
-  <si>
-    <t>胡建华</t>
-  </si>
-  <si>
-    <t>胡静</t>
-  </si>
-  <si>
-    <t>胡军</t>
-  </si>
-  <si>
-    <t>胡磊</t>
-  </si>
-  <si>
-    <t>胡明</t>
-  </si>
-  <si>
-    <t>胡涛</t>
-  </si>
-  <si>
-    <t>胡秀英</t>
-  </si>
-  <si>
-    <t>胡洋</t>
-  </si>
-  <si>
-    <t>胡志强</t>
-  </si>
-  <si>
-    <t>林超</t>
-  </si>
-  <si>
-    <t>林桂英</t>
-  </si>
-  <si>
-    <t>林杰</t>
-  </si>
-  <si>
-    <t>林静</t>
-  </si>
-  <si>
-    <t>林磊</t>
-  </si>
-  <si>
-    <t>林明</t>
-  </si>
-  <si>
-    <t>林强</t>
-  </si>
-  <si>
-    <t>林伟</t>
-  </si>
-  <si>
-    <t>林勇</t>
-  </si>
-  <si>
-    <t>刘超</t>
-  </si>
-  <si>
-    <t>刘芳</t>
-  </si>
-  <si>
-    <t>刘建华</t>
-  </si>
-  <si>
-    <t>刘静</t>
-  </si>
-  <si>
-    <t>刘军</t>
-  </si>
-  <si>
-    <t>刘磊</t>
-  </si>
-  <si>
-    <t>刘丽</t>
-  </si>
-  <si>
-    <t>刘娜</t>
-  </si>
-  <si>
-    <t>刘伟</t>
-  </si>
-  <si>
-    <t>刘勇</t>
-  </si>
-  <si>
-    <t>李桂英</t>
-  </si>
-  <si>
-    <t>李建华</t>
-  </si>
-  <si>
-    <t>李杰</t>
-  </si>
-  <si>
-    <t>李明</t>
-  </si>
-  <si>
-    <t>李强</t>
-  </si>
-  <si>
-    <t>李伟</t>
-  </si>
-  <si>
-    <t>李秀英</t>
-  </si>
-  <si>
-    <t>李艳</t>
-  </si>
-  <si>
-    <t>李洋</t>
-  </si>
-  <si>
-    <t>李勇</t>
-  </si>
-  <si>
-    <t>李志强</t>
-  </si>
-  <si>
-    <t>罗建华</t>
-  </si>
-  <si>
-    <t>罗杰</t>
-  </si>
-  <si>
-    <t>罗静</t>
-  </si>
-  <si>
-    <t>罗军</t>
-  </si>
-  <si>
-    <t>罗丽</t>
-  </si>
-  <si>
-    <t>罗明</t>
-  </si>
-  <si>
-    <t>罗娜</t>
-  </si>
-  <si>
-    <t>罗强</t>
-  </si>
-  <si>
-    <t>罗涛</t>
-  </si>
-  <si>
-    <t>罗伟</t>
-  </si>
-  <si>
-    <t>罗洋</t>
-  </si>
-  <si>
-    <t>罗勇</t>
-  </si>
-  <si>
-    <t>马芳</t>
-  </si>
-  <si>
-    <t>马军</t>
-  </si>
-  <si>
-    <t>马敏</t>
-  </si>
-  <si>
-    <t>马明</t>
-  </si>
-  <si>
-    <t>马强</t>
-  </si>
-  <si>
-    <t>马涛</t>
-  </si>
-  <si>
-    <t>马伟</t>
-  </si>
-  <si>
-    <t>马秀英</t>
-  </si>
-  <si>
-    <t>马艳</t>
-  </si>
-  <si>
-    <t>孙超</t>
-  </si>
-  <si>
-    <t>孙芳</t>
-  </si>
-  <si>
-    <t>孙桂英</t>
-  </si>
-  <si>
-    <t>孙杰</t>
-  </si>
-  <si>
-    <t>孙静</t>
-  </si>
-  <si>
-    <t>孙强</t>
-  </si>
-  <si>
-    <t>孙洋</t>
-  </si>
-  <si>
-    <t>孙勇</t>
-  </si>
-  <si>
-    <t>王桂英</t>
-  </si>
-  <si>
-    <t>王杰</t>
-  </si>
-  <si>
-    <t>王静</t>
-  </si>
-  <si>
-    <t>王军</t>
-  </si>
-  <si>
-    <t>王丽</t>
-  </si>
-  <si>
-    <t>王敏</t>
-  </si>
-  <si>
-    <t>王明</t>
-  </si>
-  <si>
-    <t>王强</t>
-  </si>
-  <si>
-    <t>王伟</t>
-  </si>
-  <si>
-    <t>王秀英</t>
-  </si>
-  <si>
-    <t>王艳</t>
-  </si>
-  <si>
-    <t>王洋</t>
-  </si>
-  <si>
-    <t>王勇</t>
-  </si>
-  <si>
-    <t>吴超</t>
-  </si>
-  <si>
-    <t>吴芳</t>
-  </si>
-  <si>
-    <t>吴建华</t>
-  </si>
-  <si>
-    <t>吴杰</t>
-  </si>
-  <si>
-    <t>吴静</t>
-  </si>
-  <si>
-    <t>吴军</t>
-  </si>
-  <si>
-    <t>吴磊</t>
-  </si>
-  <si>
-    <t>吴敏</t>
-  </si>
-  <si>
-    <t>吴娜</t>
-  </si>
-  <si>
-    <t>吴涛</t>
-  </si>
-  <si>
-    <t>吴秀英</t>
-  </si>
-  <si>
-    <t>吴艳</t>
-  </si>
-  <si>
-    <t>徐超</t>
-  </si>
-  <si>
-    <t>徐芳</t>
-  </si>
-  <si>
-    <t>徐桂英</t>
-  </si>
-  <si>
-    <t>徐丽</t>
-  </si>
-  <si>
-    <t>徐涛</t>
-  </si>
-  <si>
-    <t>徐秀英</t>
-  </si>
-  <si>
-    <t>徐艳</t>
-  </si>
-  <si>
-    <t>徐洋</t>
-  </si>
-  <si>
-    <t>杨超</t>
-  </si>
-  <si>
-    <t>杨建华</t>
-  </si>
-  <si>
-    <t>杨杰</t>
-  </si>
-  <si>
-    <t>杨磊</t>
-  </si>
-  <si>
-    <t>杨敏</t>
-  </si>
-  <si>
-    <t>杨明</t>
-  </si>
-  <si>
-    <t>杨伟</t>
-  </si>
-  <si>
-    <t>杨秀英</t>
-  </si>
-  <si>
-    <t>杨洋</t>
-  </si>
-  <si>
-    <t>张超</t>
-  </si>
-  <si>
-    <t>张杰</t>
-  </si>
-  <si>
-    <t>张丽</t>
-  </si>
-  <si>
-    <t>张敏</t>
-  </si>
-  <si>
-    <t>张娜</t>
-  </si>
-  <si>
-    <t>张强</t>
-  </si>
-  <si>
-    <t>张洋</t>
-  </si>
-  <si>
-    <t>赵超</t>
-  </si>
-  <si>
-    <t>赵静</t>
-  </si>
-  <si>
-    <t>赵丽</t>
-  </si>
-  <si>
-    <t>赵敏</t>
-  </si>
-  <si>
-    <t>赵强</t>
-  </si>
-  <si>
-    <t>赵涛</t>
-  </si>
-  <si>
-    <t>赵洋</t>
-  </si>
-  <si>
-    <t>周建华</t>
-  </si>
-  <si>
-    <t>周杰</t>
-  </si>
-  <si>
-    <t>周静</t>
-  </si>
-  <si>
-    <t>周军</t>
-  </si>
-  <si>
-    <t>周丽</t>
-  </si>
-  <si>
-    <t>周敏</t>
-  </si>
-  <si>
-    <t>周明</t>
-  </si>
-  <si>
-    <t>周涛</t>
-  </si>
-  <si>
-    <t>周秀英</t>
-  </si>
-  <si>
-    <t>周洋</t>
-  </si>
-  <si>
-    <t>朱超</t>
-  </si>
-  <si>
-    <t>朱芳</t>
-  </si>
-  <si>
-    <t>朱建华</t>
-  </si>
-  <si>
-    <t>朱杰</t>
-  </si>
-  <si>
-    <t>朱静</t>
-  </si>
-  <si>
-    <t>朱磊</t>
-  </si>
-  <si>
-    <t>朱强</t>
-  </si>
-  <si>
-    <t>朱伟</t>
-  </si>
-  <si>
-    <t>朱秀英</t>
-  </si>
-  <si>
-    <t>朱勇</t>
-  </si>
-  <si>
     <t>出生年月日</t>
   </si>
   <si>
@@ -1809,6 +1227,588 @@
   </si>
   <si>
     <t>2024.10.04</t>
+  </si>
+  <si>
+    <t>姓名1</t>
+  </si>
+  <si>
+    <t>姓名2</t>
+  </si>
+  <si>
+    <t>姓名3</t>
+  </si>
+  <si>
+    <t>姓名4</t>
+  </si>
+  <si>
+    <t>姓名5</t>
+  </si>
+  <si>
+    <t>姓名6</t>
+  </si>
+  <si>
+    <t>姓名7</t>
+  </si>
+  <si>
+    <t>姓名8</t>
+  </si>
+  <si>
+    <t>姓名9</t>
+  </si>
+  <si>
+    <t>姓名10</t>
+  </si>
+  <si>
+    <t>姓名11</t>
+  </si>
+  <si>
+    <t>姓名12</t>
+  </si>
+  <si>
+    <t>姓名13</t>
+  </si>
+  <si>
+    <t>姓名14</t>
+  </si>
+  <si>
+    <t>姓名15</t>
+  </si>
+  <si>
+    <t>姓名16</t>
+  </si>
+  <si>
+    <t>姓名17</t>
+  </si>
+  <si>
+    <t>姓名18</t>
+  </si>
+  <si>
+    <t>姓名19</t>
+  </si>
+  <si>
+    <t>姓名20</t>
+  </si>
+  <si>
+    <t>姓名21</t>
+  </si>
+  <si>
+    <t>姓名22</t>
+  </si>
+  <si>
+    <t>姓名23</t>
+  </si>
+  <si>
+    <t>姓名24</t>
+  </si>
+  <si>
+    <t>姓名25</t>
+  </si>
+  <si>
+    <t>姓名26</t>
+  </si>
+  <si>
+    <t>姓名27</t>
+  </si>
+  <si>
+    <t>姓名28</t>
+  </si>
+  <si>
+    <t>姓名29</t>
+  </si>
+  <si>
+    <t>姓名30</t>
+  </si>
+  <si>
+    <t>姓名31</t>
+  </si>
+  <si>
+    <t>姓名32</t>
+  </si>
+  <si>
+    <t>姓名33</t>
+  </si>
+  <si>
+    <t>姓名34</t>
+  </si>
+  <si>
+    <t>姓名35</t>
+  </si>
+  <si>
+    <t>姓名36</t>
+  </si>
+  <si>
+    <t>姓名37</t>
+  </si>
+  <si>
+    <t>姓名38</t>
+  </si>
+  <si>
+    <t>姓名39</t>
+  </si>
+  <si>
+    <t>姓名40</t>
+  </si>
+  <si>
+    <t>姓名41</t>
+  </si>
+  <si>
+    <t>姓名42</t>
+  </si>
+  <si>
+    <t>姓名43</t>
+  </si>
+  <si>
+    <t>姓名44</t>
+  </si>
+  <si>
+    <t>姓名45</t>
+  </si>
+  <si>
+    <t>姓名46</t>
+  </si>
+  <si>
+    <t>姓名47</t>
+  </si>
+  <si>
+    <t>姓名48</t>
+  </si>
+  <si>
+    <t>姓名49</t>
+  </si>
+  <si>
+    <t>姓名50</t>
+  </si>
+  <si>
+    <t>姓名51</t>
+  </si>
+  <si>
+    <t>姓名52</t>
+  </si>
+  <si>
+    <t>姓名53</t>
+  </si>
+  <si>
+    <t>姓名54</t>
+  </si>
+  <si>
+    <t>姓名55</t>
+  </si>
+  <si>
+    <t>姓名56</t>
+  </si>
+  <si>
+    <t>姓名57</t>
+  </si>
+  <si>
+    <t>姓名58</t>
+  </si>
+  <si>
+    <t>姓名59</t>
+  </si>
+  <si>
+    <t>姓名60</t>
+  </si>
+  <si>
+    <t>姓名61</t>
+  </si>
+  <si>
+    <t>姓名62</t>
+  </si>
+  <si>
+    <t>姓名63</t>
+  </si>
+  <si>
+    <t>姓名64</t>
+  </si>
+  <si>
+    <t>姓名65</t>
+  </si>
+  <si>
+    <t>姓名66</t>
+  </si>
+  <si>
+    <t>姓名67</t>
+  </si>
+  <si>
+    <t>姓名68</t>
+  </si>
+  <si>
+    <t>姓名69</t>
+  </si>
+  <si>
+    <t>姓名70</t>
+  </si>
+  <si>
+    <t>姓名71</t>
+  </si>
+  <si>
+    <t>姓名72</t>
+  </si>
+  <si>
+    <t>姓名73</t>
+  </si>
+  <si>
+    <t>姓名74</t>
+  </si>
+  <si>
+    <t>姓名75</t>
+  </si>
+  <si>
+    <t>姓名76</t>
+  </si>
+  <si>
+    <t>姓名77</t>
+  </si>
+  <si>
+    <t>姓名78</t>
+  </si>
+  <si>
+    <t>姓名79</t>
+  </si>
+  <si>
+    <t>姓名80</t>
+  </si>
+  <si>
+    <t>姓名81</t>
+  </si>
+  <si>
+    <t>姓名82</t>
+  </si>
+  <si>
+    <t>姓名83</t>
+  </si>
+  <si>
+    <t>姓名84</t>
+  </si>
+  <si>
+    <t>姓名85</t>
+  </si>
+  <si>
+    <t>姓名86</t>
+  </si>
+  <si>
+    <t>姓名87</t>
+  </si>
+  <si>
+    <t>姓名88</t>
+  </si>
+  <si>
+    <t>姓名89</t>
+  </si>
+  <si>
+    <t>姓名90</t>
+  </si>
+  <si>
+    <t>姓名91</t>
+  </si>
+  <si>
+    <t>姓名92</t>
+  </si>
+  <si>
+    <t>姓名93</t>
+  </si>
+  <si>
+    <t>姓名94</t>
+  </si>
+  <si>
+    <t>姓名95</t>
+  </si>
+  <si>
+    <t>姓名96</t>
+  </si>
+  <si>
+    <t>姓名97</t>
+  </si>
+  <si>
+    <t>姓名98</t>
+  </si>
+  <si>
+    <t>姓名99</t>
+  </si>
+  <si>
+    <t>姓名100</t>
+  </si>
+  <si>
+    <t>姓名101</t>
+  </si>
+  <si>
+    <t>姓名102</t>
+  </si>
+  <si>
+    <t>姓名103</t>
+  </si>
+  <si>
+    <t>姓名104</t>
+  </si>
+  <si>
+    <t>姓名105</t>
+  </si>
+  <si>
+    <t>姓名106</t>
+  </si>
+  <si>
+    <t>姓名107</t>
+  </si>
+  <si>
+    <t>姓名108</t>
+  </si>
+  <si>
+    <t>姓名109</t>
+  </si>
+  <si>
+    <t>姓名110</t>
+  </si>
+  <si>
+    <t>姓名111</t>
+  </si>
+  <si>
+    <t>姓名112</t>
+  </si>
+  <si>
+    <t>姓名113</t>
+  </si>
+  <si>
+    <t>姓名114</t>
+  </si>
+  <si>
+    <t>姓名115</t>
+  </si>
+  <si>
+    <t>姓名116</t>
+  </si>
+  <si>
+    <t>姓名117</t>
+  </si>
+  <si>
+    <t>姓名118</t>
+  </si>
+  <si>
+    <t>姓名119</t>
+  </si>
+  <si>
+    <t>姓名120</t>
+  </si>
+  <si>
+    <t>姓名121</t>
+  </si>
+  <si>
+    <t>姓名122</t>
+  </si>
+  <si>
+    <t>姓名123</t>
+  </si>
+  <si>
+    <t>姓名124</t>
+  </si>
+  <si>
+    <t>姓名125</t>
+  </si>
+  <si>
+    <t>姓名126</t>
+  </si>
+  <si>
+    <t>姓名127</t>
+  </si>
+  <si>
+    <t>姓名128</t>
+  </si>
+  <si>
+    <t>姓名129</t>
+  </si>
+  <si>
+    <t>姓名130</t>
+  </si>
+  <si>
+    <t>姓名131</t>
+  </si>
+  <si>
+    <t>姓名132</t>
+  </si>
+  <si>
+    <t>姓名133</t>
+  </si>
+  <si>
+    <t>姓名134</t>
+  </si>
+  <si>
+    <t>姓名135</t>
+  </si>
+  <si>
+    <t>姓名136</t>
+  </si>
+  <si>
+    <t>姓名137</t>
+  </si>
+  <si>
+    <t>姓名138</t>
+  </si>
+  <si>
+    <t>姓名139</t>
+  </si>
+  <si>
+    <t>姓名140</t>
+  </si>
+  <si>
+    <t>姓名141</t>
+  </si>
+  <si>
+    <t>姓名142</t>
+  </si>
+  <si>
+    <t>姓名143</t>
+  </si>
+  <si>
+    <t>姓名144</t>
+  </si>
+  <si>
+    <t>姓名145</t>
+  </si>
+  <si>
+    <t>姓名146</t>
+  </si>
+  <si>
+    <t>姓名147</t>
+  </si>
+  <si>
+    <t>姓名148</t>
+  </si>
+  <si>
+    <t>姓名149</t>
+  </si>
+  <si>
+    <t>姓名150</t>
+  </si>
+  <si>
+    <t>姓名151</t>
+  </si>
+  <si>
+    <t>姓名152</t>
+  </si>
+  <si>
+    <t>姓名153</t>
+  </si>
+  <si>
+    <t>姓名154</t>
+  </si>
+  <si>
+    <t>姓名155</t>
+  </si>
+  <si>
+    <t>姓名156</t>
+  </si>
+  <si>
+    <t>姓名157</t>
+  </si>
+  <si>
+    <t>姓名158</t>
+  </si>
+  <si>
+    <t>姓名159</t>
+  </si>
+  <si>
+    <t>姓名160</t>
+  </si>
+  <si>
+    <t>姓名161</t>
+  </si>
+  <si>
+    <t>姓名162</t>
+  </si>
+  <si>
+    <t>姓名163</t>
+  </si>
+  <si>
+    <t>姓名164</t>
+  </si>
+  <si>
+    <t>姓名165</t>
+  </si>
+  <si>
+    <t>姓名166</t>
+  </si>
+  <si>
+    <t>姓名167</t>
+  </si>
+  <si>
+    <t>姓名168</t>
+  </si>
+  <si>
+    <t>姓名169</t>
+  </si>
+  <si>
+    <t>姓名170</t>
+  </si>
+  <si>
+    <t>姓名171</t>
+  </si>
+  <si>
+    <t>姓名172</t>
+  </si>
+  <si>
+    <t>姓名173</t>
+  </si>
+  <si>
+    <t>姓名174</t>
+  </si>
+  <si>
+    <t>姓名175</t>
+  </si>
+  <si>
+    <t>姓名176</t>
+  </si>
+  <si>
+    <t>姓名177</t>
+  </si>
+  <si>
+    <t>姓名178</t>
+  </si>
+  <si>
+    <t>姓名179</t>
+  </si>
+  <si>
+    <t>姓名180</t>
+  </si>
+  <si>
+    <t>姓名181</t>
+  </si>
+  <si>
+    <t>姓名182</t>
+  </si>
+  <si>
+    <t>姓名183</t>
+  </si>
+  <si>
+    <t>姓名184</t>
+  </si>
+  <si>
+    <t>姓名185</t>
+  </si>
+  <si>
+    <t>姓名186</t>
+  </si>
+  <si>
+    <t>姓名187</t>
+  </si>
+  <si>
+    <t>姓名188</t>
+  </si>
+  <si>
+    <t>姓名189</t>
+  </si>
+  <si>
+    <t>姓名190</t>
+  </si>
+  <si>
+    <t>姓名191</t>
+  </si>
+  <si>
+    <t>姓名192</t>
+  </si>
+  <si>
+    <t>姓名193</t>
+  </si>
+  <si>
+    <t>姓名194</t>
   </si>
 </sst>
 </file>
@@ -2418,7 +2418,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>3</v>
@@ -2515,14 +2515,14 @@
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>20</v>
+      <c r="B3" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>215</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>411</v>
+        <v>217</v>
       </c>
       <c r="F3" s="2">
         <v>1</v>
@@ -2532,14 +2532,14 @@
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
+      <c r="B4" s="1" t="s">
+        <v>399</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>412</v>
+        <v>218</v>
       </c>
       <c r="F4" s="2">
         <v>2</v>
@@ -2549,14 +2549,14 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
+      <c r="B5" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>217</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>413</v>
+        <v>219</v>
       </c>
       <c r="F5" s="2">
         <v>2</v>
@@ -2566,14 +2566,14 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>22</v>
+      <c r="B6" s="1" t="s">
+        <v>400</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>218</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>414</v>
+        <v>220</v>
       </c>
       <c r="F6" s="2">
         <v>3</v>
@@ -2583,14 +2583,14 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>23</v>
+      <c r="B7" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>219</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>415</v>
+        <v>221</v>
       </c>
       <c r="F7" s="2">
         <v>3</v>
@@ -2600,14 +2600,14 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>23</v>
+      <c r="B8" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>219</v>
+        <v>25</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>416</v>
+        <v>222</v>
       </c>
       <c r="F8" s="2">
         <v>4</v>
@@ -2617,14 +2617,14 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>24</v>
+      <c r="B9" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>220</v>
+        <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>417</v>
+        <v>223</v>
       </c>
       <c r="F9" s="2">
         <v>4</v>
@@ -2634,14 +2634,14 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>25</v>
+      <c r="B10" s="1" t="s">
+        <v>403</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>221</v>
+        <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="F10" s="2">
         <v>6</v>
@@ -2651,14 +2651,14 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>26</v>
+      <c r="B11" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>411</v>
+        <v>217</v>
       </c>
       <c r="F11" s="2">
         <v>4</v>
@@ -2668,14 +2668,14 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>26</v>
+      <c r="B12" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>419</v>
+        <v>225</v>
       </c>
       <c r="F12" s="2">
         <v>4</v>
@@ -2685,14 +2685,14 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>27</v>
+      <c r="B13" s="1" t="s">
+        <v>405</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>223</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>420</v>
+        <v>226</v>
       </c>
       <c r="F13" s="2">
         <v>2</v>
@@ -2702,14 +2702,14 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>28</v>
+      <c r="B14" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>224</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>421</v>
+        <v>227</v>
       </c>
       <c r="F14" s="2">
         <v>4</v>
@@ -2719,14 +2719,14 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>29</v>
+      <c r="B15" s="1" t="s">
+        <v>407</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>225</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>422</v>
+        <v>228</v>
       </c>
       <c r="F15" s="2">
         <v>2</v>
@@ -2736,14 +2736,14 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>29</v>
+      <c r="B16" s="1" t="s">
+        <v>407</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>226</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>423</v>
+        <v>229</v>
       </c>
       <c r="F16" s="2">
         <v>4</v>
@@ -2753,14 +2753,14 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>30</v>
+      <c r="B17" s="1" t="s">
+        <v>408</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>227</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>424</v>
+        <v>230</v>
       </c>
       <c r="F17" s="2">
         <v>4</v>
@@ -2770,14 +2770,14 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>30</v>
+      <c r="B18" s="1" t="s">
+        <v>408</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>227</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>425</v>
+        <v>231</v>
       </c>
       <c r="F18" s="2">
         <v>4</v>
@@ -2787,14 +2787,14 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>31</v>
+      <c r="B19" s="1" t="s">
+        <v>409</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>228</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>426</v>
+        <v>232</v>
       </c>
       <c r="F19" s="2">
         <v>2</v>
@@ -2804,14 +2804,14 @@
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>31</v>
+      <c r="B20" s="1" t="s">
+        <v>409</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>229</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>427</v>
+        <v>233</v>
       </c>
       <c r="F20" s="2">
         <v>6</v>
@@ -2821,14 +2821,14 @@
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>32</v>
+      <c r="B21" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>428</v>
+        <v>234</v>
       </c>
       <c r="F21" s="2">
         <v>3</v>
@@ -2838,14 +2838,14 @@
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>32</v>
+      <c r="B22" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>231</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>429</v>
+        <v>235</v>
       </c>
       <c r="F22" s="2">
         <v>3</v>
@@ -2855,14 +2855,14 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>32</v>
+      <c r="B23" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>430</v>
+        <v>236</v>
       </c>
       <c r="F23" s="2">
         <v>3</v>
@@ -2872,14 +2872,14 @@
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>32</v>
+      <c r="B24" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>431</v>
+        <v>237</v>
       </c>
       <c r="F24" s="2">
         <v>3</v>
@@ -2889,14 +2889,14 @@
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>32</v>
+      <c r="B25" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>231</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>432</v>
+        <v>238</v>
       </c>
       <c r="F25" s="2">
         <v>3</v>
@@ -2906,14 +2906,14 @@
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>32</v>
+      <c r="B26" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>231</v>
+        <v>37</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>433</v>
+        <v>239</v>
       </c>
       <c r="F26" s="2">
         <v>3</v>
@@ -2923,14 +2923,14 @@
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>32</v>
+      <c r="B27" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>434</v>
+        <v>240</v>
       </c>
       <c r="F27" s="2">
         <v>4</v>
@@ -2940,14 +2940,14 @@
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>32</v>
+      <c r="B28" s="1" t="s">
+        <v>410</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>435</v>
+        <v>241</v>
       </c>
       <c r="F28" s="2">
         <v>4</v>
@@ -2957,14 +2957,14 @@
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>33</v>
+      <c r="B29" s="1" t="s">
+        <v>411</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>232</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>436</v>
+        <v>242</v>
       </c>
       <c r="F29" s="2">
         <v>2</v>
@@ -2974,14 +2974,14 @@
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>33</v>
+      <c r="B30" s="1" t="s">
+        <v>411</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>233</v>
+        <v>39</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>421</v>
+        <v>227</v>
       </c>
       <c r="F30" s="2">
         <v>1</v>
@@ -2991,14 +2991,14 @@
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>33</v>
+      <c r="B31" s="1" t="s">
+        <v>411</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>234</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>437</v>
+        <v>243</v>
       </c>
       <c r="F31" s="2">
         <v>4</v>
@@ -3008,14 +3008,14 @@
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>34</v>
+      <c r="B32" s="1" t="s">
+        <v>412</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>235</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>438</v>
+        <v>244</v>
       </c>
       <c r="F32" s="2">
         <v>2</v>
@@ -3025,14 +3025,14 @@
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>35</v>
+      <c r="B33" s="1" t="s">
+        <v>413</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>236</v>
+        <v>42</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>439</v>
+        <v>245</v>
       </c>
       <c r="F33" s="2">
         <v>4</v>
@@ -3042,14 +3042,14 @@
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>36</v>
+      <c r="B34" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>237</v>
+        <v>43</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>440</v>
+        <v>246</v>
       </c>
       <c r="F34" s="2">
         <v>2</v>
@@ -3059,14 +3059,14 @@
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>36</v>
+      <c r="B35" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>237</v>
+        <v>43</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>441</v>
+        <v>247</v>
       </c>
       <c r="F35" s="2">
         <v>2</v>
@@ -3076,14 +3076,14 @@
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>37</v>
+      <c r="B36" s="1" t="s">
+        <v>415</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>238</v>
+        <v>44</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>417</v>
+        <v>223</v>
       </c>
       <c r="F36" s="2">
         <v>2</v>
@@ -3093,14 +3093,14 @@
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>38</v>
+      <c r="B37" s="1" t="s">
+        <v>416</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>228</v>
+        <v>34</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>442</v>
+        <v>248</v>
       </c>
       <c r="F37" s="2">
         <v>3</v>
@@ -3110,14 +3110,14 @@
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>39</v>
+      <c r="B38" s="1" t="s">
+        <v>417</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>224</v>
+        <v>30</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>323</v>
+        <v>129</v>
       </c>
       <c r="F38" s="2">
         <v>4</v>
@@ -3127,14 +3127,14 @@
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>40</v>
+      <c r="B39" s="1" t="s">
+        <v>418</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>239</v>
+        <v>45</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>413</v>
+        <v>219</v>
       </c>
       <c r="F39" s="2">
         <v>3</v>
@@ -3144,14 +3144,14 @@
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>41</v>
+      <c r="B40" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>240</v>
+        <v>46</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>443</v>
+        <v>249</v>
       </c>
       <c r="F40" s="2">
         <v>3</v>
@@ -3161,14 +3161,14 @@
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>41</v>
+      <c r="B41" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>240</v>
+        <v>46</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>444</v>
+        <v>250</v>
       </c>
       <c r="F41" s="2">
         <v>4</v>
@@ -3178,14 +3178,14 @@
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>42</v>
+      <c r="B42" s="1" t="s">
+        <v>420</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>241</v>
+        <v>47</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>422</v>
+        <v>228</v>
       </c>
       <c r="F42" s="2">
         <v>6</v>
@@ -3195,14 +3195,14 @@
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>42</v>
+      <c r="B43" s="1" t="s">
+        <v>420</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>242</v>
+        <v>48</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>445</v>
+        <v>251</v>
       </c>
       <c r="F43" s="2">
         <v>4</v>
@@ -3212,48 +3212,48 @@
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>43</v>
+      <c r="B44" s="1" t="s">
+        <v>421</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>243</v>
+        <v>49</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>446</v>
+        <v>252</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>447</v>
+        <v>253</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>43</v>
+      <c r="B45" s="1" t="s">
+        <v>421</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>243</v>
+        <v>49</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>448</v>
+        <v>254</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>447</v>
+        <v>253</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>44</v>
+      <c r="B46" s="1" t="s">
+        <v>422</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>244</v>
+        <v>50</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>449</v>
+        <v>255</v>
       </c>
       <c r="F46" s="2">
         <v>3</v>
@@ -3263,14 +3263,14 @@
       <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>44</v>
+      <c r="B47" s="1" t="s">
+        <v>422</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>245</v>
+        <v>51</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>450</v>
+        <v>256</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -3280,14 +3280,14 @@
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>44</v>
+      <c r="B48" s="1" t="s">
+        <v>422</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>245</v>
+        <v>51</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>419</v>
+        <v>225</v>
       </c>
       <c r="F48" s="2">
         <v>1</v>
@@ -3297,14 +3297,14 @@
       <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>45</v>
+      <c r="B49" s="1" t="s">
+        <v>423</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>246</v>
+        <v>52</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>451</v>
+        <v>257</v>
       </c>
       <c r="F49" s="2">
         <v>3</v>
@@ -3314,14 +3314,14 @@
       <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>45</v>
+      <c r="B50" s="1" t="s">
+        <v>423</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>247</v>
+        <v>53</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>452</v>
+        <v>258</v>
       </c>
       <c r="F50" s="2">
         <v>5</v>
@@ -3331,14 +3331,14 @@
       <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>45</v>
+      <c r="B51" s="1" t="s">
+        <v>423</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>246</v>
+        <v>52</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>450</v>
+        <v>256</v>
       </c>
       <c r="F51" s="2">
         <v>4</v>
@@ -3348,14 +3348,14 @@
       <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>46</v>
+      <c r="B52" s="1" t="s">
+        <v>424</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>234</v>
+        <v>40</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>453</v>
+        <v>259</v>
       </c>
       <c r="F52" s="2">
         <v>3</v>
@@ -3365,14 +3365,14 @@
       <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>47</v>
+      <c r="B53" s="1" t="s">
+        <v>425</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>248</v>
+        <v>54</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>417</v>
+        <v>223</v>
       </c>
       <c r="F53" s="2">
         <v>1</v>
@@ -3382,14 +3382,14 @@
       <c r="A54" s="1">
         <v>52</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>48</v>
+      <c r="B54" s="1" t="s">
+        <v>426</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>224</v>
+        <v>30</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>454</v>
+        <v>260</v>
       </c>
       <c r="F54" s="2">
         <v>4</v>
@@ -3399,14 +3399,14 @@
       <c r="A55" s="1">
         <v>53</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>49</v>
+      <c r="B55" s="1" t="s">
+        <v>427</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>249</v>
+        <v>55</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>455</v>
+        <v>261</v>
       </c>
       <c r="F55" s="2">
         <v>3</v>
@@ -3416,14 +3416,14 @@
       <c r="A56" s="1">
         <v>54</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>49</v>
+      <c r="B56" s="1" t="s">
+        <v>427</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>250</v>
+        <v>56</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>456</v>
+        <v>262</v>
       </c>
       <c r="F56" s="2">
         <v>2</v>
@@ -3433,14 +3433,14 @@
       <c r="A57" s="1">
         <v>55</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>49</v>
+      <c r="B57" s="1" t="s">
+        <v>427</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>249</v>
+        <v>55</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>457</v>
+        <v>263</v>
       </c>
       <c r="F57" s="2">
         <v>3</v>
@@ -3450,14 +3450,14 @@
       <c r="A58" s="1">
         <v>56</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>49</v>
+      <c r="B58" s="1" t="s">
+        <v>427</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>249</v>
+        <v>55</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>458</v>
+        <v>264</v>
       </c>
       <c r="F58" s="2">
         <v>3</v>
@@ -3467,14 +3467,14 @@
       <c r="A59" s="1">
         <v>57</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>49</v>
+      <c r="B59" s="1" t="s">
+        <v>427</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>249</v>
+        <v>55</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>459</v>
+        <v>265</v>
       </c>
       <c r="F59" s="2">
         <v>3</v>
@@ -3484,14 +3484,14 @@
       <c r="A60" s="1">
         <v>58</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>50</v>
+      <c r="B60" s="1" t="s">
+        <v>428</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>251</v>
+        <v>57</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>460</v>
+        <v>266</v>
       </c>
       <c r="F60" s="2">
         <v>4</v>
@@ -3501,14 +3501,14 @@
       <c r="A61" s="1">
         <v>59</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>50</v>
+      <c r="B61" s="1" t="s">
+        <v>428</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>251</v>
+        <v>57</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>461</v>
+        <v>267</v>
       </c>
       <c r="F61" s="2">
         <v>4</v>
@@ -3518,14 +3518,14 @@
       <c r="A62" s="1">
         <v>60</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>50</v>
+      <c r="B62" s="1" t="s">
+        <v>428</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>251</v>
+        <v>57</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>462</v>
+        <v>268</v>
       </c>
       <c r="F62" s="2">
         <v>5</v>
@@ -3535,48 +3535,48 @@
       <c r="A63" s="1">
         <v>61</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>51</v>
+      <c r="B63" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>252</v>
+        <v>58</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>463</v>
+        <v>269</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>447</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="1">
         <v>62</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>51</v>
+      <c r="B64" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>252</v>
+        <v>58</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>464</v>
+        <v>270</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>447</v>
+        <v>253</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65" s="1">
         <v>63</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>51</v>
+      <c r="B65" s="1" t="s">
+        <v>429</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>253</v>
+        <v>59</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>465</v>
+        <v>271</v>
       </c>
       <c r="F65" s="2">
         <v>3</v>
@@ -3586,14 +3586,14 @@
       <c r="A66" s="1">
         <v>64</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>52</v>
+      <c r="B66" s="1" t="s">
+        <v>430</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>254</v>
+        <v>60</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>466</v>
+        <v>272</v>
       </c>
       <c r="F66" s="2">
         <v>2</v>
@@ -3603,14 +3603,14 @@
       <c r="A67" s="1">
         <v>65</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>52</v>
+      <c r="B67" s="1" t="s">
+        <v>430</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>255</v>
+        <v>61</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>467</v>
+        <v>273</v>
       </c>
       <c r="F67" s="2">
         <v>2</v>
@@ -3620,14 +3620,14 @@
       <c r="A68" s="1">
         <v>66</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>53</v>
+      <c r="B68" s="1" t="s">
+        <v>431</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>256</v>
+        <v>62</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>468</v>
+        <v>274</v>
       </c>
       <c r="F68" s="2">
         <v>2</v>
@@ -3637,14 +3637,14 @@
       <c r="A69" s="1">
         <v>67</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>53</v>
+      <c r="B69" s="1" t="s">
+        <v>431</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>257</v>
+        <v>63</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>469</v>
+        <v>275</v>
       </c>
       <c r="F69" s="2">
         <v>3</v>
@@ -3654,14 +3654,14 @@
       <c r="A70" s="1">
         <v>68</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>54</v>
+      <c r="B70" s="1" t="s">
+        <v>432</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>255</v>
+        <v>61</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>470</v>
+        <v>276</v>
       </c>
       <c r="F70" s="2">
         <v>2</v>
@@ -3671,14 +3671,14 @@
       <c r="A71" s="1">
         <v>69</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>55</v>
+      <c r="B71" s="1" t="s">
+        <v>433</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>258</v>
+        <v>64</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>471</v>
+        <v>277</v>
       </c>
       <c r="F71" s="2">
         <v>2</v>
@@ -3688,14 +3688,14 @@
       <c r="A72" s="1">
         <v>70</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>55</v>
+      <c r="B72" s="1" t="s">
+        <v>433</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>259</v>
+        <v>65</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>472</v>
+        <v>278</v>
       </c>
       <c r="F72" s="2">
         <v>2</v>
@@ -3705,14 +3705,14 @@
       <c r="A73" s="1">
         <v>71</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>56</v>
+      <c r="B73" s="1" t="s">
+        <v>434</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>260</v>
+        <v>66</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>449</v>
+        <v>255</v>
       </c>
       <c r="F73" s="2">
         <v>3</v>
@@ -3722,14 +3722,14 @@
       <c r="A74" s="1">
         <v>72</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>57</v>
+      <c r="B74" s="1" t="s">
+        <v>435</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>261</v>
+        <v>67</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>456</v>
+        <v>262</v>
       </c>
       <c r="F74" s="2">
         <v>2</v>
@@ -3739,14 +3739,14 @@
       <c r="A75" s="1">
         <v>73</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>57</v>
+      <c r="B75" s="1" t="s">
+        <v>435</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>262</v>
+        <v>68</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>420</v>
+        <v>226</v>
       </c>
       <c r="F75" s="2">
         <v>2</v>
@@ -3756,14 +3756,14 @@
       <c r="A76" s="1">
         <v>74</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>58</v>
+      <c r="B76" s="1" t="s">
+        <v>436</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>263</v>
+        <v>69</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>473</v>
+        <v>279</v>
       </c>
       <c r="F76" s="2">
         <v>1</v>
@@ -3773,14 +3773,14 @@
       <c r="A77" s="1">
         <v>75</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>58</v>
+      <c r="B77" s="1" t="s">
+        <v>436</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>263</v>
+        <v>69</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>474</v>
+        <v>280</v>
       </c>
       <c r="F77" s="2">
         <v>1</v>
@@ -3790,14 +3790,14 @@
       <c r="A78" s="1">
         <v>76</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>58</v>
+      <c r="B78" s="1" t="s">
+        <v>436</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>264</v>
+        <v>70</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>475</v>
+        <v>281</v>
       </c>
       <c r="F78" s="2">
         <v>5</v>
@@ -3807,14 +3807,14 @@
       <c r="A79" s="1">
         <v>77</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>58</v>
+      <c r="B79" s="1" t="s">
+        <v>436</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>265</v>
+        <v>71</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>476</v>
+        <v>282</v>
       </c>
       <c r="F79" s="2">
         <v>2</v>
@@ -3824,14 +3824,14 @@
       <c r="A80" s="1">
         <v>78</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>59</v>
+      <c r="B80" s="1" t="s">
+        <v>437</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>266</v>
+        <v>72</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>477</v>
+        <v>283</v>
       </c>
       <c r="F80" s="2">
         <v>5</v>
@@ -3841,14 +3841,14 @@
       <c r="A81" s="1">
         <v>79</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>60</v>
+      <c r="B81" s="1" t="s">
+        <v>438</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>267</v>
+        <v>73</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>478</v>
+        <v>284</v>
       </c>
       <c r="F81" s="2">
         <v>1</v>
@@ -3858,14 +3858,14 @@
       <c r="A82" s="1">
         <v>80</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>61</v>
+      <c r="B82" s="1" t="s">
+        <v>439</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>268</v>
+        <v>74</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>479</v>
+        <v>285</v>
       </c>
       <c r="F82" s="2">
         <v>6</v>
@@ -3875,14 +3875,14 @@
       <c r="A83" s="1">
         <v>81</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>62</v>
+      <c r="B83" s="1" t="s">
+        <v>440</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>269</v>
+        <v>75</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>480</v>
+        <v>286</v>
       </c>
       <c r="F83" s="2">
         <v>4</v>
@@ -3892,14 +3892,14 @@
       <c r="A84" s="1">
         <v>82</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>63</v>
+      <c r="B84" s="1" t="s">
+        <v>441</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>270</v>
+        <v>76</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>481</v>
+        <v>287</v>
       </c>
       <c r="F84" s="2">
         <v>6</v>
@@ -3909,14 +3909,14 @@
       <c r="A85" s="1">
         <v>83</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>64</v>
+      <c r="B85" s="1" t="s">
+        <v>442</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>482</v>
+        <v>288</v>
       </c>
       <c r="F85" s="2">
         <v>4</v>
@@ -3926,14 +3926,14 @@
       <c r="A86" s="1">
         <v>84</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>65</v>
+      <c r="B86" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>272</v>
+        <v>78</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>421</v>
+        <v>227</v>
       </c>
       <c r="F86" s="2">
         <v>6</v>
@@ -3943,14 +3943,14 @@
       <c r="A87" s="1">
         <v>85</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>65</v>
+      <c r="B87" s="1" t="s">
+        <v>443</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>423</v>
+        <v>229</v>
       </c>
       <c r="F87" s="2">
         <v>5</v>
@@ -3960,14 +3960,14 @@
       <c r="A88" s="1">
         <v>86</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>66</v>
+      <c r="B88" s="1" t="s">
+        <v>444</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>274</v>
+        <v>80</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>477</v>
+        <v>283</v>
       </c>
       <c r="F88" s="2">
         <v>1</v>
@@ -3977,14 +3977,14 @@
       <c r="A89" s="1">
         <v>87</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>67</v>
+      <c r="B89" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>437</v>
+        <v>243</v>
       </c>
       <c r="F89" s="2">
         <v>2</v>
@@ -3994,14 +3994,14 @@
       <c r="A90" s="1">
         <v>88</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>68</v>
+      <c r="B90" s="1" t="s">
+        <v>446</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>479</v>
+        <v>285</v>
       </c>
       <c r="F90" s="2">
         <v>3</v>
@@ -4011,14 +4011,14 @@
       <c r="A91" s="1">
         <v>89</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>68</v>
+      <c r="B91" s="1" t="s">
+        <v>446</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>483</v>
+        <v>289</v>
       </c>
       <c r="F91" s="2">
         <v>2</v>
@@ -4028,14 +4028,14 @@
       <c r="A92" s="1">
         <v>90</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>69</v>
+      <c r="B92" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>484</v>
+        <v>290</v>
       </c>
       <c r="F92" s="2">
         <v>3</v>
@@ -4045,14 +4045,14 @@
       <c r="A93" s="1">
         <v>91</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>69</v>
+      <c r="B93" s="1" t="s">
+        <v>447</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>485</v>
+        <v>291</v>
       </c>
       <c r="F93" s="2">
         <v>2</v>
@@ -4062,14 +4062,14 @@
       <c r="A94" s="1">
         <v>92</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>70</v>
+      <c r="B94" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>279</v>
+        <v>85</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>486</v>
+        <v>292</v>
       </c>
       <c r="F94" s="2">
         <v>2</v>
@@ -4079,14 +4079,14 @@
       <c r="A95" s="1">
         <v>93</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>70</v>
+      <c r="B95" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>280</v>
+        <v>86</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>487</v>
+        <v>293</v>
       </c>
       <c r="F95" s="2">
         <v>2</v>
@@ -4096,14 +4096,14 @@
       <c r="A96" s="1">
         <v>94</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>70</v>
+      <c r="B96" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>280</v>
+        <v>86</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>488</v>
+        <v>294</v>
       </c>
       <c r="F96" s="2">
         <v>2</v>
@@ -4113,14 +4113,14 @@
       <c r="A97" s="1">
         <v>95</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>70</v>
+      <c r="B97" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>281</v>
+        <v>87</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>489</v>
+        <v>295</v>
       </c>
       <c r="F97" s="2">
         <v>2</v>
@@ -4130,14 +4130,14 @@
       <c r="A98" s="1">
         <v>96</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>70</v>
+      <c r="B98" s="1" t="s">
+        <v>448</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>280</v>
+        <v>86</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>490</v>
+        <v>296</v>
       </c>
       <c r="F98" s="2">
         <v>3</v>
@@ -4147,14 +4147,14 @@
       <c r="A99" s="1">
         <v>97</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>71</v>
+      <c r="B99" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>485</v>
+        <v>291</v>
       </c>
       <c r="F99" s="2">
         <v>2</v>
@@ -4164,14 +4164,14 @@
       <c r="A100" s="1">
         <v>98</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>71</v>
+      <c r="B100" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>282</v>
+        <v>88</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>491</v>
+        <v>297</v>
       </c>
       <c r="F100" s="2">
         <v>4</v>
@@ -4181,14 +4181,14 @@
       <c r="A101" s="1">
         <v>99</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>71</v>
+      <c r="B101" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>282</v>
+        <v>88</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>416</v>
+        <v>222</v>
       </c>
       <c r="F101" s="2">
         <v>4</v>
@@ -4198,14 +4198,14 @@
       <c r="A102" s="1">
         <v>100</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>71</v>
+      <c r="B102" s="1" t="s">
+        <v>449</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>282</v>
+        <v>88</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>492</v>
+        <v>298</v>
       </c>
       <c r="F102" s="2">
         <v>4</v>
@@ -4215,14 +4215,14 @@
       <c r="A103" s="1">
         <v>101</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>72</v>
+      <c r="B103" s="1" t="s">
+        <v>450</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>283</v>
+        <v>89</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>493</v>
+        <v>299</v>
       </c>
       <c r="F103" s="2">
         <v>6</v>
@@ -4232,14 +4232,14 @@
       <c r="A104" s="1">
         <v>102</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>73</v>
+      <c r="B104" s="1" t="s">
+        <v>451</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>284</v>
+        <v>90</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>494</v>
+        <v>300</v>
       </c>
       <c r="F104" s="2">
         <v>4</v>
@@ -4249,14 +4249,14 @@
       <c r="A105" s="1">
         <v>103</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>74</v>
+      <c r="B105" s="1" t="s">
+        <v>452</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>269</v>
+        <v>75</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>411</v>
+        <v>217</v>
       </c>
       <c r="F105" s="2">
         <v>5</v>
@@ -4266,14 +4266,14 @@
       <c r="A106" s="1">
         <v>104</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>74</v>
+      <c r="B106" s="1" t="s">
+        <v>452</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>269</v>
+        <v>75</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>495</v>
+        <v>301</v>
       </c>
       <c r="F106" s="2">
         <v>5</v>
@@ -4283,14 +4283,14 @@
       <c r="A107" s="1">
         <v>105</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>74</v>
+      <c r="B107" s="1" t="s">
+        <v>452</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>269</v>
+        <v>75</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>419</v>
+        <v>225</v>
       </c>
       <c r="F107" s="2">
         <v>5</v>
@@ -4300,14 +4300,14 @@
       <c r="A108" s="1">
         <v>106</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>75</v>
+      <c r="B108" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>285</v>
+        <v>91</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>496</v>
+        <v>302</v>
       </c>
       <c r="F108" s="2">
         <v>3</v>
@@ -4317,14 +4317,14 @@
       <c r="A109" s="1">
         <v>107</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>75</v>
+      <c r="B109" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>286</v>
+        <v>92</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>485</v>
+        <v>291</v>
       </c>
       <c r="F109" s="2">
         <v>2</v>
@@ -4334,14 +4334,14 @@
       <c r="A110" s="1">
         <v>108</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>75</v>
+      <c r="B110" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>286</v>
+        <v>92</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>482</v>
+        <v>288</v>
       </c>
       <c r="F110" s="2">
         <v>3</v>
@@ -4351,14 +4351,14 @@
       <c r="A111" s="1">
         <v>109</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>75</v>
+      <c r="B111" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>285</v>
+        <v>91</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>411</v>
+        <v>217</v>
       </c>
       <c r="F111" s="2">
         <v>3</v>
@@ -4368,14 +4368,14 @@
       <c r="A112" s="1">
         <v>110</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>75</v>
+      <c r="B112" s="1" t="s">
+        <v>453</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>287</v>
+        <v>93</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>423</v>
+        <v>229</v>
       </c>
       <c r="F112" s="2">
         <v>3</v>
@@ -4385,14 +4385,14 @@
       <c r="A113" s="1">
         <v>111</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>76</v>
+      <c r="B113" s="1" t="s">
+        <v>454</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>288</v>
+        <v>94</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>497</v>
+        <v>303</v>
       </c>
       <c r="F113" s="2">
         <v>3</v>
@@ -4402,14 +4402,14 @@
       <c r="A114" s="1">
         <v>112</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>77</v>
+      <c r="B114" s="1" t="s">
+        <v>455</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>433</v>
+        <v>239</v>
       </c>
       <c r="F114" s="2">
         <v>5</v>
@@ -4419,14 +4419,14 @@
       <c r="A115" s="1">
         <v>113</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>78</v>
+      <c r="B115" s="1" t="s">
+        <v>456</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>485</v>
+        <v>291</v>
       </c>
       <c r="F115" s="2">
         <v>4</v>
@@ -4436,14 +4436,14 @@
       <c r="A116" s="1">
         <v>114</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>78</v>
+      <c r="B116" s="1" t="s">
+        <v>456</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>249</v>
+        <v>55</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>498</v>
+        <v>304</v>
       </c>
       <c r="F116" s="2">
         <v>3</v>
@@ -4453,14 +4453,14 @@
       <c r="A117" s="1">
         <v>115</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>78</v>
+      <c r="B117" s="1" t="s">
+        <v>456</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>249</v>
+        <v>55</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>499</v>
+        <v>305</v>
       </c>
       <c r="F117" s="2">
         <v>3</v>
@@ -4470,14 +4470,14 @@
       <c r="A118" s="1">
         <v>116</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>78</v>
+      <c r="B118" s="1" t="s">
+        <v>456</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>249</v>
+        <v>55</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>500</v>
+        <v>306</v>
       </c>
       <c r="F118" s="2">
         <v>3</v>
@@ -4487,14 +4487,14 @@
       <c r="A119" s="1">
         <v>117</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>79</v>
+      <c r="B119" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>290</v>
+        <v>96</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>413</v>
+        <v>219</v>
       </c>
       <c r="F119" s="2">
         <v>1</v>
@@ -4504,14 +4504,14 @@
       <c r="A120" s="1">
         <v>118</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>79</v>
+      <c r="B120" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>291</v>
+        <v>97</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>426</v>
+        <v>232</v>
       </c>
       <c r="F120" s="2">
         <v>4</v>
@@ -4521,14 +4521,14 @@
       <c r="A121" s="1">
         <v>119</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>79</v>
+      <c r="B121" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>291</v>
+        <v>97</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>501</v>
+        <v>307</v>
       </c>
       <c r="F121" s="2">
         <v>4</v>
@@ -4538,14 +4538,14 @@
       <c r="A122" s="1">
         <v>120</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>79</v>
+      <c r="B122" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>291</v>
+        <v>97</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>456</v>
+        <v>262</v>
       </c>
       <c r="F122" s="2">
         <v>5</v>
@@ -4555,14 +4555,14 @@
       <c r="A123" s="1">
         <v>121</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>80</v>
+      <c r="B123" s="1" t="s">
+        <v>458</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>292</v>
+        <v>98</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>502</v>
+        <v>308</v>
       </c>
       <c r="F123" s="2">
         <v>7</v>
@@ -4572,14 +4572,14 @@
       <c r="A124" s="1">
         <v>122</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>80</v>
+      <c r="B124" s="1" t="s">
+        <v>458</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>233</v>
+        <v>39</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>411</v>
+        <v>217</v>
       </c>
       <c r="F124" s="2">
         <v>1</v>
@@ -4589,14 +4589,14 @@
       <c r="A125" s="1">
         <v>123</v>
       </c>
-      <c r="B125" s="2" t="s">
-        <v>81</v>
+      <c r="B125" s="1" t="s">
+        <v>459</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>293</v>
+        <v>99</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>415</v>
+        <v>221</v>
       </c>
       <c r="F125" s="2">
         <v>3</v>
@@ -4606,14 +4606,14 @@
       <c r="A126" s="1">
         <v>124</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>82</v>
+      <c r="B126" s="1" t="s">
+        <v>460</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>477</v>
+        <v>283</v>
       </c>
       <c r="F126" s="2">
         <v>1</v>
@@ -4623,14 +4623,14 @@
       <c r="A127" s="1">
         <v>125</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>83</v>
+      <c r="B127" s="1" t="s">
+        <v>461</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>294</v>
+        <v>100</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>443</v>
+        <v>249</v>
       </c>
       <c r="F127" s="2">
         <v>3</v>
@@ -4640,14 +4640,14 @@
       <c r="A128" s="1">
         <v>126</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>84</v>
+      <c r="B128" s="1" t="s">
+        <v>462</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>295</v>
+        <v>101</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>503</v>
+        <v>309</v>
       </c>
       <c r="F128" s="2">
         <v>6</v>
@@ -4657,14 +4657,14 @@
       <c r="A129" s="1">
         <v>127</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>84</v>
+      <c r="B129" s="1" t="s">
+        <v>462</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>296</v>
+        <v>102</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>504</v>
+        <v>310</v>
       </c>
       <c r="F129" s="2">
         <v>3</v>
@@ -4674,14 +4674,14 @@
       <c r="A130" s="1">
         <v>128</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>84</v>
+      <c r="B130" s="1" t="s">
+        <v>462</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>296</v>
+        <v>102</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>421</v>
+        <v>227</v>
       </c>
       <c r="F130" s="2">
         <v>3</v>
@@ -4691,14 +4691,14 @@
       <c r="A131" s="1">
         <v>129</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>85</v>
+      <c r="B131" s="1" t="s">
+        <v>463</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>257</v>
+        <v>63</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>469</v>
+        <v>275</v>
       </c>
       <c r="F131" s="2">
         <v>3</v>
@@ -4708,14 +4708,14 @@
       <c r="A132" s="1">
         <v>130</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>86</v>
+      <c r="B132" s="1" t="s">
+        <v>464</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>297</v>
+        <v>103</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>505</v>
+        <v>311</v>
       </c>
       <c r="F132" s="2">
         <v>5</v>
@@ -4725,14 +4725,14 @@
       <c r="A133" s="1">
         <v>131</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>86</v>
+      <c r="B133" s="1" t="s">
+        <v>464</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>298</v>
+        <v>104</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>506</v>
+        <v>312</v>
       </c>
       <c r="F133" s="2">
         <v>2</v>
@@ -4742,14 +4742,14 @@
       <c r="A134" s="1">
         <v>132</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>86</v>
+      <c r="B134" s="1" t="s">
+        <v>464</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>298</v>
+        <v>104</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>507</v>
+        <v>313</v>
       </c>
       <c r="F134" s="2">
         <v>2</v>
@@ -4759,14 +4759,14 @@
       <c r="A135" s="1">
         <v>133</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>87</v>
+      <c r="B135" s="1" t="s">
+        <v>465</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>480</v>
+        <v>286</v>
       </c>
       <c r="F135" s="2">
         <v>3</v>
@@ -4776,14 +4776,14 @@
       <c r="A136" s="1">
         <v>134</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>88</v>
+      <c r="B136" s="1" t="s">
+        <v>466</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>300</v>
+        <v>106</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>508</v>
+        <v>314</v>
       </c>
       <c r="F136" s="2">
         <v>2</v>
@@ -4793,14 +4793,14 @@
       <c r="A137" s="1">
         <v>135</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>89</v>
+      <c r="B137" s="1" t="s">
+        <v>467</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>301</v>
+        <v>107</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>443</v>
+        <v>249</v>
       </c>
       <c r="F137" s="2">
         <v>2</v>
@@ -4810,14 +4810,14 @@
       <c r="A138" s="1">
         <v>136</v>
       </c>
-      <c r="B138" s="2" t="s">
-        <v>89</v>
+      <c r="B138" s="1" t="s">
+        <v>467</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>302</v>
+        <v>108</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>509</v>
+        <v>315</v>
       </c>
       <c r="F138" s="2">
         <v>2</v>
@@ -4827,14 +4827,14 @@
       <c r="A139" s="1">
         <v>137</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>90</v>
+      <c r="B139" s="1" t="s">
+        <v>468</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>303</v>
+        <v>109</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>510</v>
+        <v>316</v>
       </c>
       <c r="F139" s="2">
         <v>3</v>
@@ -4844,14 +4844,14 @@
       <c r="A140" s="1">
         <v>138</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>91</v>
+      <c r="B140" s="1" t="s">
+        <v>469</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>304</v>
+        <v>110</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>486</v>
+        <v>292</v>
       </c>
       <c r="F140" s="2">
         <v>5</v>
@@ -4861,14 +4861,14 @@
       <c r="A141" s="1">
         <v>139</v>
       </c>
-      <c r="B141" s="2" t="s">
-        <v>91</v>
+      <c r="B141" s="1" t="s">
+        <v>469</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>239</v>
+        <v>45</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>465</v>
+        <v>271</v>
       </c>
       <c r="F141" s="2">
         <v>3</v>
@@ -4878,14 +4878,14 @@
       <c r="A142" s="1">
         <v>140</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>92</v>
+      <c r="B142" s="1" t="s">
+        <v>470</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>225</v>
+        <v>31</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>511</v>
+        <v>317</v>
       </c>
       <c r="F142" s="2">
         <v>2</v>
@@ -4895,14 +4895,14 @@
       <c r="A143" s="1">
         <v>141</v>
       </c>
-      <c r="B143" s="2" t="s">
-        <v>92</v>
+      <c r="B143" s="1" t="s">
+        <v>470</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>225</v>
+        <v>31</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>512</v>
+        <v>318</v>
       </c>
       <c r="F143" s="2">
         <v>3</v>
@@ -4912,14 +4912,14 @@
       <c r="A144" s="1">
         <v>142</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>92</v>
+      <c r="B144" s="1" t="s">
+        <v>470</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>500</v>
+        <v>306</v>
       </c>
       <c r="F144" s="2">
         <v>4</v>
@@ -4929,31 +4929,31 @@
       <c r="A145" s="1">
         <v>143</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>93</v>
+      <c r="B145" s="1" t="s">
+        <v>471</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>306</v>
+        <v>112</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>513</v>
+        <v>319</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>447</v>
+        <v>253</v>
       </c>
     </row>
     <row r="146" spans="1:6">
       <c r="A146" s="1">
         <v>144</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>94</v>
+      <c r="B146" s="1" t="s">
+        <v>472</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>307</v>
+        <v>113</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>514</v>
+        <v>320</v>
       </c>
       <c r="F146" s="2">
         <v>1</v>
@@ -4963,14 +4963,14 @@
       <c r="A147" s="1">
         <v>145</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>95</v>
+      <c r="B147" s="1" t="s">
+        <v>473</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>515</v>
+        <v>321</v>
       </c>
       <c r="F147" s="2">
         <v>3</v>
@@ -4980,14 +4980,14 @@
       <c r="A148" s="1">
         <v>146</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>95</v>
+      <c r="B148" s="1" t="s">
+        <v>473</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>308</v>
+        <v>114</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>516</v>
+        <v>322</v>
       </c>
       <c r="F148" s="2">
         <v>2</v>
@@ -4997,14 +4997,14 @@
       <c r="A149" s="1">
         <v>147</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>96</v>
+      <c r="B149" s="1" t="s">
+        <v>474</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>309</v>
+        <v>115</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>500</v>
+        <v>306</v>
       </c>
       <c r="F149" s="2">
         <v>3</v>
@@ -5014,14 +5014,14 @@
       <c r="A150" s="1">
         <v>148</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>96</v>
+      <c r="B150" s="1" t="s">
+        <v>474</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>309</v>
+        <v>115</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>517</v>
+        <v>323</v>
       </c>
       <c r="F150" s="2">
         <v>3</v>
@@ -5031,14 +5031,14 @@
       <c r="A151" s="1">
         <v>149</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>97</v>
+      <c r="B151" s="1" t="s">
+        <v>475</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>310</v>
+        <v>116</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>512</v>
+        <v>318</v>
       </c>
       <c r="F151" s="2">
         <v>2</v>
@@ -5048,14 +5048,14 @@
       <c r="A152" s="1">
         <v>150</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>97</v>
+      <c r="B152" s="1" t="s">
+        <v>475</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>482</v>
+        <v>288</v>
       </c>
       <c r="F152" s="2">
         <v>3</v>
@@ -5065,14 +5065,14 @@
       <c r="A153" s="1">
         <v>151</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>98</v>
+      <c r="B153" s="1" t="s">
+        <v>476</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>311</v>
+        <v>117</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>502</v>
+        <v>308</v>
       </c>
       <c r="F153" s="2">
         <v>2</v>
@@ -5082,14 +5082,14 @@
       <c r="A154" s="1">
         <v>152</v>
       </c>
-      <c r="B154" s="2" t="s">
-        <v>98</v>
+      <c r="B154" s="1" t="s">
+        <v>476</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>250</v>
+        <v>56</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>494</v>
+        <v>300</v>
       </c>
       <c r="F154" s="2">
         <v>2</v>
@@ -5099,14 +5099,14 @@
       <c r="A155" s="1">
         <v>153</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>98</v>
+      <c r="B155" s="1" t="s">
+        <v>476</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>510</v>
+        <v>316</v>
       </c>
       <c r="F155" s="2">
         <v>3</v>
@@ -5116,14 +5116,14 @@
       <c r="A156" s="1">
         <v>154</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>98</v>
+      <c r="B156" s="1" t="s">
+        <v>476</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>278</v>
+        <v>84</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>491</v>
+        <v>297</v>
       </c>
       <c r="F156" s="2">
         <v>4</v>
@@ -5133,14 +5133,14 @@
       <c r="A157" s="1">
         <v>155</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>99</v>
+      <c r="B157" s="1" t="s">
+        <v>477</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>312</v>
+        <v>118</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>456</v>
+        <v>262</v>
       </c>
       <c r="F157" s="2">
         <v>3</v>
@@ -5150,14 +5150,14 @@
       <c r="A158" s="1">
         <v>156</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>99</v>
+      <c r="B158" s="1" t="s">
+        <v>477</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>312</v>
+        <v>118</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>416</v>
+        <v>222</v>
       </c>
       <c r="F158" s="2">
         <v>4</v>
@@ -5167,14 +5167,14 @@
       <c r="A159" s="1">
         <v>157</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>99</v>
+      <c r="B159" s="1" t="s">
+        <v>477</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>312</v>
+        <v>118</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>518</v>
+        <v>324</v>
       </c>
       <c r="F159" s="2">
         <v>4</v>
@@ -5184,14 +5184,14 @@
       <c r="A160" s="1">
         <v>158</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>100</v>
+      <c r="B160" s="1" t="s">
+        <v>478</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>313</v>
+        <v>119</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>411</v>
+        <v>217</v>
       </c>
       <c r="F160" s="2">
         <v>1</v>
@@ -5201,14 +5201,14 @@
       <c r="A161" s="1">
         <v>159</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>101</v>
+      <c r="B161" s="1" t="s">
+        <v>479</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>519</v>
+        <v>325</v>
       </c>
       <c r="F161" s="2">
         <v>4</v>
@@ -5218,14 +5218,14 @@
       <c r="A162" s="1">
         <v>160</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>102</v>
+      <c r="B162" s="1" t="s">
+        <v>480</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>315</v>
+        <v>121</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>520</v>
+        <v>326</v>
       </c>
       <c r="F162" s="2">
         <v>2</v>
@@ -5235,14 +5235,14 @@
       <c r="A163" s="1">
         <v>161</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>103</v>
+      <c r="B163" s="1" t="s">
+        <v>481</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>316</v>
+        <v>122</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>521</v>
+        <v>327</v>
       </c>
       <c r="F163" s="2">
         <v>1</v>
@@ -5252,14 +5252,14 @@
       <c r="A164" s="1">
         <v>162</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>104</v>
+      <c r="B164" s="1" t="s">
+        <v>482</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>317</v>
+        <v>123</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>491</v>
+        <v>297</v>
       </c>
       <c r="F164" s="2">
         <v>2</v>
@@ -5269,14 +5269,14 @@
       <c r="A165" s="1">
         <v>163</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>105</v>
+      <c r="B165" s="1" t="s">
+        <v>483</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>318</v>
+        <v>124</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>522</v>
+        <v>328</v>
       </c>
       <c r="F165" s="2">
         <v>2</v>
@@ -5286,14 +5286,14 @@
       <c r="A166" s="1">
         <v>164</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>106</v>
+      <c r="B166" s="1" t="s">
+        <v>484</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>264</v>
+        <v>70</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>523</v>
+        <v>329</v>
       </c>
       <c r="F166" s="2">
         <v>6</v>
@@ -5303,14 +5303,14 @@
       <c r="A167" s="1">
         <v>165</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>107</v>
+      <c r="B167" s="1" t="s">
+        <v>485</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>319</v>
+        <v>125</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>524</v>
+        <v>330</v>
       </c>
       <c r="F167" s="2">
         <v>3</v>
@@ -5320,14 +5320,14 @@
       <c r="A168" s="1">
         <v>166</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>108</v>
+      <c r="B168" s="1" t="s">
+        <v>486</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>525</v>
+        <v>331</v>
       </c>
       <c r="F168" s="2">
         <v>2</v>
@@ -5337,14 +5337,14 @@
       <c r="A169" s="1">
         <v>167</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>108</v>
+      <c r="B169" s="1" t="s">
+        <v>486</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>470</v>
+        <v>276</v>
       </c>
       <c r="F169" s="2">
         <v>2</v>
@@ -5354,14 +5354,14 @@
       <c r="A170" s="1">
         <v>168</v>
       </c>
-      <c r="B170" s="2" t="s">
-        <v>108</v>
+      <c r="B170" s="1" t="s">
+        <v>486</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>450</v>
+        <v>256</v>
       </c>
       <c r="F170" s="2">
         <v>2</v>
@@ -5371,14 +5371,14 @@
       <c r="A171" s="1">
         <v>169</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>109</v>
+      <c r="B171" s="1" t="s">
+        <v>487</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>320</v>
+        <v>126</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>526</v>
+        <v>332</v>
       </c>
       <c r="F171" s="2">
         <v>2</v>
@@ -5388,14 +5388,14 @@
       <c r="A172" s="1">
         <v>170</v>
       </c>
-      <c r="B172" s="2" t="s">
-        <v>109</v>
+      <c r="B172" s="1" t="s">
+        <v>487</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>320</v>
+        <v>126</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>527</v>
+        <v>333</v>
       </c>
       <c r="F172" s="2">
         <v>3</v>
@@ -5405,14 +5405,14 @@
       <c r="A173" s="1">
         <v>171</v>
       </c>
-      <c r="B173" s="2" t="s">
-        <v>110</v>
+      <c r="B173" s="1" t="s">
+        <v>488</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>321</v>
+        <v>127</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>528</v>
+        <v>334</v>
       </c>
       <c r="F173" s="2">
         <v>4</v>
@@ -5422,14 +5422,14 @@
       <c r="A174" s="1">
         <v>172</v>
       </c>
-      <c r="B174" s="2" t="s">
-        <v>110</v>
+      <c r="B174" s="1" t="s">
+        <v>488</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>321</v>
+        <v>127</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>457</v>
+        <v>263</v>
       </c>
       <c r="F174" s="2">
         <v>4</v>
@@ -5439,14 +5439,14 @@
       <c r="A175" s="1">
         <v>173</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>111</v>
+      <c r="B175" s="1" t="s">
+        <v>489</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>318</v>
+        <v>124</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>529</v>
+        <v>335</v>
       </c>
       <c r="F175" s="2">
         <v>1</v>
@@ -5456,14 +5456,14 @@
       <c r="A176" s="1">
         <v>174</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>111</v>
+      <c r="B176" s="1" t="s">
+        <v>489</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>322</v>
+        <v>128</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>517</v>
+        <v>323</v>
       </c>
       <c r="F176" s="2">
         <v>5</v>
@@ -5473,14 +5473,14 @@
       <c r="A177" s="1">
         <v>175</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>112</v>
+      <c r="B177" s="1" t="s">
+        <v>490</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>280</v>
+        <v>86</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>323</v>
+        <v>129</v>
       </c>
       <c r="F177" s="2">
         <v>2</v>
@@ -5490,14 +5490,14 @@
       <c r="A178" s="1">
         <v>176</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>112</v>
+      <c r="B178" s="1" t="s">
+        <v>490</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>303</v>
+        <v>109</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>464</v>
+        <v>270</v>
       </c>
       <c r="F178" s="2">
         <v>2</v>
@@ -5507,14 +5507,14 @@
       <c r="A179" s="1">
         <v>177</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>113</v>
+      <c r="B179" s="1" t="s">
+        <v>491</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>322</v>
+        <v>128</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>530</v>
+        <v>336</v>
       </c>
       <c r="F179" s="2">
         <v>4</v>
@@ -5524,14 +5524,14 @@
       <c r="A180" s="1">
         <v>178</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>113</v>
+      <c r="B180" s="1" t="s">
+        <v>491</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>323</v>
+        <v>129</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>531</v>
+        <v>337</v>
       </c>
       <c r="F180" s="2">
         <v>1</v>
@@ -5541,14 +5541,14 @@
       <c r="A181" s="1">
         <v>179</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>114</v>
+      <c r="B181" s="1" t="s">
+        <v>492</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>324</v>
+        <v>130</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>532</v>
+        <v>338</v>
       </c>
       <c r="F181" s="2">
         <v>3</v>
@@ -5558,14 +5558,14 @@
       <c r="A182" s="1">
         <v>180</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>115</v>
+      <c r="B182" s="1" t="s">
+        <v>493</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>275</v>
+        <v>81</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>486</v>
+        <v>292</v>
       </c>
       <c r="F182" s="2">
         <v>1</v>
@@ -5575,14 +5575,14 @@
       <c r="A183" s="1">
         <v>181</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>115</v>
+      <c r="B183" s="1" t="s">
+        <v>493</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>322</v>
+        <v>128</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>413</v>
+        <v>219</v>
       </c>
       <c r="F183" s="2">
         <v>4</v>
@@ -5592,14 +5592,14 @@
       <c r="A184" s="1">
         <v>182</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>115</v>
+      <c r="B184" s="1" t="s">
+        <v>493</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>325</v>
+        <v>131</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>533</v>
+        <v>339</v>
       </c>
       <c r="F184" s="2">
         <v>2</v>
@@ -5609,14 +5609,14 @@
       <c r="A185" s="1">
         <v>183</v>
       </c>
-      <c r="B185" s="2" t="s">
-        <v>116</v>
+      <c r="B185" s="1" t="s">
+        <v>494</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>326</v>
+        <v>132</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>518</v>
+        <v>324</v>
       </c>
       <c r="F185" s="2">
         <v>2</v>
@@ -5626,14 +5626,14 @@
       <c r="A186" s="1">
         <v>184</v>
       </c>
-      <c r="B186" s="2" t="s">
-        <v>117</v>
+      <c r="B186" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="D186" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E186" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="E186" s="2" t="s">
-        <v>521</v>
       </c>
       <c r="F186" s="2">
         <v>6</v>
@@ -5643,14 +5643,14 @@
       <c r="A187" s="1">
         <v>185</v>
       </c>
-      <c r="B187" s="2" t="s">
-        <v>117</v>
+      <c r="B187" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>328</v>
+        <v>134</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>534</v>
+        <v>340</v>
       </c>
       <c r="F187" s="2">
         <v>4</v>
@@ -5660,14 +5660,14 @@
       <c r="A188" s="1">
         <v>186</v>
       </c>
-      <c r="B188" s="2" t="s">
-        <v>117</v>
+      <c r="B188" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>329</v>
+        <v>135</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>494</v>
+        <v>300</v>
       </c>
       <c r="F188" s="2">
         <v>1</v>
@@ -5677,14 +5677,14 @@
       <c r="A189" s="1">
         <v>187</v>
       </c>
-      <c r="B189" s="2" t="s">
+      <c r="B189" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="D189" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D189" s="3" t="s">
-        <v>312</v>
-      </c>
       <c r="E189" s="2" t="s">
-        <v>529</v>
+        <v>335</v>
       </c>
       <c r="F189" s="2">
         <v>3</v>
@@ -5694,14 +5694,14 @@
       <c r="A190" s="1">
         <v>188</v>
       </c>
-      <c r="B190" s="2" t="s">
-        <v>119</v>
+      <c r="B190" s="1" t="s">
+        <v>497</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>224</v>
+        <v>30</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>529</v>
+        <v>335</v>
       </c>
       <c r="F190" s="2">
         <v>3</v>
@@ -5711,14 +5711,14 @@
       <c r="A191" s="1">
         <v>189</v>
       </c>
-      <c r="B191" s="2" t="s">
-        <v>119</v>
+      <c r="B191" s="1" t="s">
+        <v>497</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>330</v>
+        <v>136</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>535</v>
+        <v>341</v>
       </c>
       <c r="F191" s="2">
         <v>3</v>
@@ -5728,14 +5728,14 @@
       <c r="A192" s="1">
         <v>190</v>
       </c>
-      <c r="B192" s="2" t="s">
-        <v>120</v>
+      <c r="B192" s="1" t="s">
+        <v>498</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>331</v>
+        <v>137</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>536</v>
+        <v>342</v>
       </c>
       <c r="F192" s="2">
         <v>2</v>
@@ -5745,14 +5745,14 @@
       <c r="A193" s="1">
         <v>191</v>
       </c>
-      <c r="B193" s="2" t="s">
-        <v>121</v>
+      <c r="B193" s="1" t="s">
+        <v>499</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>332</v>
+        <v>138</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>456</v>
+        <v>262</v>
       </c>
       <c r="F193" s="2">
         <v>3</v>
@@ -5762,14 +5762,14 @@
       <c r="A194" s="1">
         <v>192</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>121</v>
+      <c r="B194" s="1" t="s">
+        <v>499</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>330</v>
+        <v>136</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>416</v>
+        <v>222</v>
       </c>
       <c r="F194" s="2">
         <v>3</v>
@@ -5779,14 +5779,14 @@
       <c r="A195" s="1">
         <v>193</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>121</v>
+      <c r="B195" s="1" t="s">
+        <v>499</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>330</v>
+        <v>136</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>533</v>
+        <v>339</v>
       </c>
       <c r="F195" s="2">
         <v>4</v>
@@ -5796,14 +5796,14 @@
       <c r="A196" s="1">
         <v>194</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>122</v>
+      <c r="B196" s="1" t="s">
+        <v>500</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>333</v>
+        <v>139</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>506</v>
+        <v>312</v>
       </c>
       <c r="F196" s="2">
         <v>4</v>
@@ -5813,14 +5813,14 @@
       <c r="A197" s="1">
         <v>195</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>123</v>
+      <c r="B197" s="1" t="s">
+        <v>501</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>284</v>
+        <v>90</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>492</v>
+        <v>298</v>
       </c>
       <c r="F197" s="2">
         <v>5</v>
@@ -5830,14 +5830,14 @@
       <c r="A198" s="1">
         <v>196</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>124</v>
+      <c r="B198" s="1" t="s">
+        <v>502</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>334</v>
+        <v>140</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>490</v>
+        <v>296</v>
       </c>
       <c r="F198" s="2">
         <v>4</v>
@@ -5847,14 +5847,14 @@
       <c r="A199" s="1">
         <v>197</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>125</v>
+      <c r="B199" s="1" t="s">
+        <v>503</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>335</v>
+        <v>141</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>537</v>
+        <v>343</v>
       </c>
       <c r="F199" s="2">
         <v>2</v>
@@ -5864,14 +5864,14 @@
       <c r="A200" s="1">
         <v>198</v>
       </c>
-      <c r="B200" s="2" t="s">
-        <v>126</v>
+      <c r="B200" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>336</v>
+        <v>142</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>497</v>
+        <v>303</v>
       </c>
       <c r="F200" s="2">
         <v>5</v>
@@ -5881,14 +5881,14 @@
       <c r="A201" s="1">
         <v>199</v>
       </c>
-      <c r="B201" s="2" t="s">
-        <v>126</v>
+      <c r="B201" s="1" t="s">
+        <v>504</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>336</v>
+        <v>142</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>423</v>
+        <v>229</v>
       </c>
       <c r="F201" s="2">
         <v>5</v>
@@ -5898,14 +5898,14 @@
       <c r="A202" s="1">
         <v>200</v>
       </c>
-      <c r="B202" s="2" t="s">
-        <v>127</v>
+      <c r="B202" s="1" t="s">
+        <v>505</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>337</v>
+        <v>143</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>477</v>
+        <v>283</v>
       </c>
       <c r="F202" s="2">
         <v>4</v>
@@ -5915,14 +5915,14 @@
       <c r="A203" s="1">
         <v>201</v>
       </c>
-      <c r="B203" s="2" t="s">
-        <v>128</v>
+      <c r="B203" s="1" t="s">
+        <v>506</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>338</v>
+        <v>144</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>538</v>
+        <v>344</v>
       </c>
       <c r="F203" s="2">
         <v>3</v>
@@ -5932,14 +5932,14 @@
       <c r="A204" s="1">
         <v>202</v>
       </c>
-      <c r="B204" s="2" t="s">
-        <v>128</v>
+      <c r="B204" s="1" t="s">
+        <v>506</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>339</v>
+        <v>145</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>539</v>
+        <v>345</v>
       </c>
       <c r="F204" s="2">
         <v>2</v>
@@ -5949,14 +5949,14 @@
       <c r="A205" s="1">
         <v>203</v>
       </c>
-      <c r="B205" s="2" t="s">
-        <v>128</v>
+      <c r="B205" s="1" t="s">
+        <v>506</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>338</v>
+        <v>144</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>448</v>
+        <v>254</v>
       </c>
       <c r="F205" s="2">
         <v>4</v>
@@ -5966,14 +5966,14 @@
       <c r="A206" s="1">
         <v>204</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>129</v>
+      <c r="B206" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>269</v>
+        <v>75</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>540</v>
+        <v>346</v>
       </c>
       <c r="F206" s="2">
         <v>4</v>
@@ -5983,14 +5983,14 @@
       <c r="A207" s="1">
         <v>205</v>
       </c>
-      <c r="B207" s="2" t="s">
-        <v>129</v>
+      <c r="B207" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>269</v>
+        <v>75</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>541</v>
+        <v>347</v>
       </c>
       <c r="F207" s="2">
         <v>4</v>
@@ -6000,14 +6000,14 @@
       <c r="A208" s="1">
         <v>206</v>
       </c>
-      <c r="B208" s="2" t="s">
-        <v>129</v>
+      <c r="B208" s="1" t="s">
+        <v>507</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>456</v>
+        <v>262</v>
       </c>
       <c r="F208" s="2">
         <v>2</v>
@@ -6017,14 +6017,14 @@
       <c r="A209" s="1">
         <v>207</v>
       </c>
-      <c r="B209" s="2" t="s">
-        <v>130</v>
+      <c r="B209" s="1" t="s">
+        <v>508</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>340</v>
+        <v>146</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>438</v>
+        <v>244</v>
       </c>
       <c r="F209" s="2">
         <v>4</v>
@@ -6034,14 +6034,14 @@
       <c r="A210" s="1">
         <v>208</v>
       </c>
-      <c r="B210" s="2" t="s">
-        <v>130</v>
+      <c r="B210" s="1" t="s">
+        <v>508</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>340</v>
+        <v>146</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>542</v>
+        <v>348</v>
       </c>
       <c r="F210" s="2">
         <v>5</v>
@@ -6051,14 +6051,14 @@
       <c r="A211" s="1">
         <v>209</v>
       </c>
-      <c r="B211" s="2" t="s">
-        <v>131</v>
+      <c r="B211" s="1" t="s">
+        <v>509</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>341</v>
+        <v>147</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>498</v>
+        <v>304</v>
       </c>
       <c r="F211" s="2">
         <v>3</v>
@@ -6068,14 +6068,14 @@
       <c r="A212" s="1">
         <v>210</v>
       </c>
-      <c r="B212" s="2" t="s">
-        <v>132</v>
+      <c r="B212" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>231</v>
+        <v>37</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>487</v>
+        <v>293</v>
       </c>
       <c r="F212" s="2">
         <v>3</v>
@@ -6085,14 +6085,14 @@
       <c r="A213" s="1">
         <v>211</v>
       </c>
-      <c r="B213" s="2" t="s">
-        <v>132</v>
+      <c r="B213" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>231</v>
+        <v>37</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>532</v>
+        <v>338</v>
       </c>
       <c r="F213" s="2">
         <v>4</v>
@@ -6102,14 +6102,14 @@
       <c r="A214" s="1">
         <v>212</v>
       </c>
-      <c r="B214" s="2" t="s">
-        <v>133</v>
+      <c r="B214" s="1" t="s">
+        <v>511</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>342</v>
+        <v>148</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>506</v>
+        <v>312</v>
       </c>
       <c r="F214" s="2">
         <v>2</v>
@@ -6119,14 +6119,14 @@
       <c r="A215" s="1">
         <v>213</v>
       </c>
-      <c r="B215" s="2" t="s">
-        <v>134</v>
+      <c r="B215" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>287</v>
+        <v>93</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>486</v>
+        <v>292</v>
       </c>
       <c r="F215" s="2">
         <v>1</v>
@@ -6136,14 +6136,14 @@
       <c r="A216" s="1">
         <v>214</v>
       </c>
-      <c r="B216" s="2" t="s">
-        <v>134</v>
+      <c r="B216" s="1" t="s">
+        <v>512</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>343</v>
+        <v>149</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>543</v>
+        <v>349</v>
       </c>
       <c r="F216" s="2">
         <v>4</v>
@@ -6153,14 +6153,14 @@
       <c r="A217" s="1">
         <v>215</v>
       </c>
-      <c r="B217" s="2" t="s">
-        <v>135</v>
+      <c r="B217" s="1" t="s">
+        <v>513</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>260</v>
+        <v>66</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>513</v>
+        <v>319</v>
       </c>
       <c r="F217" s="2">
         <v>3</v>
@@ -6170,14 +6170,14 @@
       <c r="A218" s="1">
         <v>216</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>136</v>
+      <c r="B218" s="1" t="s">
+        <v>514</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>344</v>
+        <v>150</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>530</v>
+        <v>336</v>
       </c>
       <c r="F218" s="2">
         <v>2</v>
@@ -6187,14 +6187,14 @@
       <c r="A219" s="1">
         <v>217</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>137</v>
+      <c r="B219" s="1" t="s">
+        <v>515</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>345</v>
+        <v>151</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>544</v>
+        <v>350</v>
       </c>
       <c r="F219" s="2">
         <v>4</v>
@@ -6204,14 +6204,14 @@
       <c r="A220" s="1">
         <v>218</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>138</v>
+      <c r="B220" s="1" t="s">
+        <v>516</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>545</v>
+        <v>351</v>
       </c>
       <c r="F220" s="2">
         <v>5</v>
@@ -6221,14 +6221,14 @@
       <c r="A221" s="1">
         <v>219</v>
       </c>
-      <c r="B221" s="2" t="s">
-        <v>139</v>
+      <c r="B221" s="1" t="s">
+        <v>517</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>346</v>
+        <v>152</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>546</v>
+        <v>352</v>
       </c>
       <c r="F221" s="2">
         <v>6</v>
@@ -6238,14 +6238,14 @@
       <c r="A222" s="1">
         <v>220</v>
       </c>
-      <c r="B222" s="2" t="s">
-        <v>140</v>
+      <c r="B222" s="1" t="s">
+        <v>518</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>347</v>
+        <v>153</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>547</v>
+        <v>353</v>
       </c>
       <c r="F222" s="2">
         <v>1</v>
@@ -6255,14 +6255,14 @@
       <c r="A223" s="1">
         <v>221</v>
       </c>
-      <c r="B223" s="2" t="s">
-        <v>141</v>
+      <c r="B223" s="1" t="s">
+        <v>519</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>506</v>
+        <v>312</v>
       </c>
       <c r="F223" s="2">
         <v>3</v>
@@ -6272,14 +6272,14 @@
       <c r="A224" s="1">
         <v>222</v>
       </c>
-      <c r="B224" s="2" t="s">
-        <v>141</v>
+      <c r="B224" s="1" t="s">
+        <v>519</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>449</v>
+        <v>255</v>
       </c>
       <c r="F224" s="2">
         <v>3</v>
@@ -6289,14 +6289,14 @@
       <c r="A225" s="1">
         <v>223</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>142</v>
+      <c r="B225" s="1" t="s">
+        <v>520</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>296</v>
+        <v>102</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>471</v>
+        <v>277</v>
       </c>
       <c r="F225" s="2">
         <v>4</v>
@@ -6306,14 +6306,14 @@
       <c r="A226" s="1">
         <v>224</v>
       </c>
-      <c r="B226" s="2" t="s">
-        <v>142</v>
+      <c r="B226" s="1" t="s">
+        <v>520</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>296</v>
+        <v>102</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>500</v>
+        <v>306</v>
       </c>
       <c r="F226" s="2">
         <v>4</v>
@@ -6323,14 +6323,14 @@
       <c r="A227" s="1">
         <v>225</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>143</v>
+      <c r="B227" s="1" t="s">
+        <v>521</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>348</v>
+        <v>154</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>548</v>
+        <v>354</v>
       </c>
       <c r="F227" s="2">
         <v>1</v>
@@ -6340,14 +6340,14 @@
       <c r="A228" s="1">
         <v>226</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>144</v>
+      <c r="B228" s="1" t="s">
+        <v>522</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>314</v>
+        <v>120</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>465</v>
+        <v>271</v>
       </c>
       <c r="F228" s="2">
         <v>3</v>
@@ -6357,14 +6357,14 @@
       <c r="A229" s="1">
         <v>227</v>
       </c>
-      <c r="B229" s="2" t="s">
-        <v>144</v>
+      <c r="B229" s="1" t="s">
+        <v>522</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>349</v>
+        <v>155</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>415</v>
+        <v>221</v>
       </c>
       <c r="F229" s="2">
         <v>2</v>
@@ -6374,14 +6374,14 @@
       <c r="A230" s="1">
         <v>228</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>144</v>
+      <c r="B230" s="1" t="s">
+        <v>522</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>350</v>
+        <v>156</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>421</v>
+        <v>227</v>
       </c>
       <c r="F230" s="2">
         <v>3</v>
@@ -6391,14 +6391,14 @@
       <c r="A231" s="1">
         <v>229</v>
       </c>
-      <c r="B231" s="2" t="s">
-        <v>144</v>
+      <c r="B231" s="1" t="s">
+        <v>522</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>350</v>
+        <v>156</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>411</v>
+        <v>217</v>
       </c>
       <c r="F231" s="2">
         <v>3</v>
@@ -6408,14 +6408,14 @@
       <c r="A232" s="1">
         <v>230</v>
       </c>
-      <c r="B232" s="2" t="s">
-        <v>145</v>
+      <c r="B232" s="1" t="s">
+        <v>523</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>351</v>
+        <v>157</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>549</v>
+        <v>355</v>
       </c>
       <c r="F232" s="2">
         <v>5</v>
@@ -6425,14 +6425,14 @@
       <c r="A233" s="1">
         <v>231</v>
       </c>
-      <c r="B233" s="2" t="s">
-        <v>145</v>
+      <c r="B233" s="1" t="s">
+        <v>523</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>352</v>
+        <v>158</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>511</v>
+        <v>317</v>
       </c>
       <c r="F233" s="2">
         <v>3</v>
@@ -6442,14 +6442,14 @@
       <c r="A234" s="1">
         <v>232</v>
       </c>
-      <c r="B234" s="2" t="s">
-        <v>145</v>
+      <c r="B234" s="1" t="s">
+        <v>523</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>351</v>
+        <v>157</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>484</v>
+        <v>290</v>
       </c>
       <c r="F234" s="2">
         <v>5</v>
@@ -6459,14 +6459,14 @@
       <c r="A235" s="1">
         <v>233</v>
       </c>
-      <c r="B235" s="2" t="s">
-        <v>145</v>
+      <c r="B235" s="1" t="s">
+        <v>523</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>353</v>
+        <v>159</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>550</v>
+        <v>356</v>
       </c>
       <c r="F235" s="2">
         <v>2</v>
@@ -6476,14 +6476,14 @@
       <c r="A236" s="1">
         <v>234</v>
       </c>
-      <c r="B236" s="2" t="s">
-        <v>146</v>
+      <c r="B236" s="1" t="s">
+        <v>524</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>354</v>
+        <v>160</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>547</v>
+        <v>353</v>
       </c>
       <c r="F236" s="2">
         <v>1</v>
@@ -6493,14 +6493,14 @@
       <c r="A237" s="1">
         <v>235</v>
       </c>
-      <c r="B237" s="2" t="s">
-        <v>146</v>
+      <c r="B237" s="1" t="s">
+        <v>524</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>355</v>
+        <v>161</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>429</v>
+        <v>235</v>
       </c>
       <c r="F237" s="2">
         <v>1</v>
@@ -6510,14 +6510,14 @@
       <c r="A238" s="1">
         <v>236</v>
       </c>
-      <c r="B238" s="2" t="s">
-        <v>146</v>
+      <c r="B238" s="1" t="s">
+        <v>524</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>355</v>
+        <v>161</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>454</v>
+        <v>260</v>
       </c>
       <c r="F238" s="2">
         <v>2</v>
@@ -6527,14 +6527,14 @@
       <c r="A239" s="1">
         <v>237</v>
       </c>
-      <c r="B239" s="2" t="s">
-        <v>146</v>
+      <c r="B239" s="1" t="s">
+        <v>524</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>355</v>
+        <v>161</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>551</v>
+        <v>357</v>
       </c>
       <c r="F239" s="2">
         <v>2</v>
@@ -6544,14 +6544,14 @@
       <c r="A240" s="1">
         <v>238</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>147</v>
+      <c r="B240" s="1" t="s">
+        <v>525</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>287</v>
+        <v>93</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>501</v>
+        <v>307</v>
       </c>
       <c r="F240" s="2">
         <v>2</v>
@@ -6561,14 +6561,14 @@
       <c r="A241" s="1">
         <v>239</v>
       </c>
-      <c r="B241" s="2" t="s">
-        <v>147</v>
+      <c r="B241" s="1" t="s">
+        <v>525</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>287</v>
+        <v>93</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>550</v>
+        <v>356</v>
       </c>
       <c r="F241" s="2">
         <v>2</v>
@@ -6578,14 +6578,14 @@
       <c r="A242" s="1">
         <v>240</v>
       </c>
-      <c r="B242" s="2" t="s">
-        <v>147</v>
+      <c r="B242" s="1" t="s">
+        <v>525</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>287</v>
+        <v>93</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>552</v>
+        <v>358</v>
       </c>
       <c r="F242" s="2">
         <v>3</v>
@@ -6595,14 +6595,14 @@
       <c r="A243" s="1">
         <v>241</v>
       </c>
-      <c r="B243" s="2" t="s">
-        <v>148</v>
+      <c r="B243" s="1" t="s">
+        <v>526</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>356</v>
+        <v>162</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>525</v>
+        <v>331</v>
       </c>
       <c r="F243" s="2">
         <v>5</v>
@@ -6612,14 +6612,14 @@
       <c r="A244" s="1">
         <v>242</v>
       </c>
-      <c r="B244" s="2" t="s">
-        <v>149</v>
+      <c r="B244" s="1" t="s">
+        <v>527</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>357</v>
+        <v>163</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>486</v>
+        <v>292</v>
       </c>
       <c r="F244" s="2">
         <v>6</v>
@@ -6629,14 +6629,14 @@
       <c r="A245" s="1">
         <v>243</v>
       </c>
-      <c r="B245" s="2" t="s">
-        <v>150</v>
+      <c r="B245" s="1" t="s">
+        <v>528</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>358</v>
+        <v>164</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>424</v>
+        <v>230</v>
       </c>
       <c r="F245" s="2">
         <v>3</v>
@@ -6646,14 +6646,14 @@
       <c r="A246" s="1">
         <v>244</v>
       </c>
-      <c r="B246" s="2" t="s">
-        <v>150</v>
+      <c r="B246" s="1" t="s">
+        <v>528</v>
       </c>
       <c r="D246" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="E246" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="F246" s="2">
         <v>3</v>
@@ -6663,14 +6663,14 @@
       <c r="A247" s="1">
         <v>245</v>
       </c>
-      <c r="B247" s="2" t="s">
-        <v>150</v>
+      <c r="B247" s="1" t="s">
+        <v>528</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>358</v>
+        <v>164</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>450</v>
+        <v>256</v>
       </c>
       <c r="F247" s="2">
         <v>3</v>
@@ -6680,14 +6680,14 @@
       <c r="A248" s="1">
         <v>246</v>
       </c>
-      <c r="B248" s="2" t="s">
-        <v>151</v>
+      <c r="B248" s="1" t="s">
+        <v>529</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>344</v>
+        <v>150</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>530</v>
+        <v>336</v>
       </c>
       <c r="F248" s="2">
         <v>2</v>
@@ -6697,14 +6697,14 @@
       <c r="A249" s="1">
         <v>247</v>
       </c>
-      <c r="B249" s="2" t="s">
-        <v>151</v>
+      <c r="B249" s="1" t="s">
+        <v>529</v>
       </c>
       <c r="D249" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E249" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="F249" s="2">
         <v>2</v>
@@ -6714,14 +6714,14 @@
       <c r="A250" s="1">
         <v>248</v>
       </c>
-      <c r="B250" s="2" t="s">
-        <v>151</v>
+      <c r="B250" s="1" t="s">
+        <v>529</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>361</v>
+        <v>167</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>542</v>
+        <v>348</v>
       </c>
       <c r="F250" s="2">
         <v>1</v>
@@ -6731,14 +6731,14 @@
       <c r="A251" s="1">
         <v>249</v>
       </c>
-      <c r="B251" s="2" t="s">
-        <v>152</v>
+      <c r="B251" s="1" t="s">
+        <v>530</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>302</v>
+        <v>108</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>555</v>
+        <v>361</v>
       </c>
       <c r="F251" s="2">
         <v>2</v>
@@ -6748,14 +6748,14 @@
       <c r="A252" s="1">
         <v>250</v>
       </c>
-      <c r="B252" s="2" t="s">
-        <v>153</v>
+      <c r="B252" s="1" t="s">
+        <v>531</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>487</v>
+        <v>293</v>
       </c>
       <c r="F252" s="2">
         <v>2</v>
@@ -6765,14 +6765,14 @@
       <c r="A253" s="1">
         <v>251</v>
       </c>
-      <c r="B253" s="2" t="s">
-        <v>153</v>
+      <c r="B253" s="1" t="s">
+        <v>531</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>539</v>
+        <v>345</v>
       </c>
       <c r="F253" s="2">
         <v>2</v>
@@ -6782,14 +6782,14 @@
       <c r="A254" s="1">
         <v>252</v>
       </c>
-      <c r="B254" s="2" t="s">
-        <v>153</v>
+      <c r="B254" s="1" t="s">
+        <v>531</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>277</v>
+        <v>83</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>556</v>
+        <v>362</v>
       </c>
       <c r="F254" s="2">
         <v>3</v>
@@ -6799,14 +6799,14 @@
       <c r="A255" s="1">
         <v>253</v>
       </c>
-      <c r="B255" s="2" t="s">
-        <v>154</v>
+      <c r="B255" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>362</v>
+        <v>168</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>451</v>
+        <v>257</v>
       </c>
       <c r="F255" s="2">
         <v>4</v>
@@ -6816,14 +6816,14 @@
       <c r="A256" s="1">
         <v>254</v>
       </c>
-      <c r="B256" s="2" t="s">
-        <v>154</v>
+      <c r="B256" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="D256" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E256" s="2" t="s">
         <v>363</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="F256" s="2">
         <v>3</v>
@@ -6833,14 +6833,14 @@
       <c r="A257" s="1">
         <v>255</v>
       </c>
-      <c r="B257" s="2" t="s">
-        <v>154</v>
+      <c r="B257" s="1" t="s">
+        <v>532</v>
       </c>
       <c r="D257" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E257" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>558</v>
       </c>
       <c r="F257" s="2">
         <v>2</v>
@@ -6850,14 +6850,14 @@
       <c r="A258" s="1">
         <v>256</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>155</v>
+      <c r="B258" s="1" t="s">
+        <v>533</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>365</v>
+        <v>171</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>546</v>
+        <v>352</v>
       </c>
       <c r="F258" s="2">
         <v>1</v>
@@ -6867,14 +6867,14 @@
       <c r="A259" s="1">
         <v>257</v>
       </c>
-      <c r="B259" s="2" t="s">
-        <v>155</v>
+      <c r="B259" s="1" t="s">
+        <v>533</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>366</v>
+        <v>172</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>499</v>
+        <v>305</v>
       </c>
       <c r="F259" s="2">
         <v>1</v>
@@ -6884,14 +6884,14 @@
       <c r="A260" s="1">
         <v>258</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>155</v>
+      <c r="B260" s="1" t="s">
+        <v>533</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>366</v>
+        <v>172</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>559</v>
+        <v>365</v>
       </c>
       <c r="F260" s="2">
         <v>1</v>
@@ -6901,14 +6901,14 @@
       <c r="A261" s="1">
         <v>259</v>
       </c>
-      <c r="B261" s="2" t="s">
-        <v>156</v>
+      <c r="B261" s="1" t="s">
+        <v>534</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>367</v>
+        <v>173</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>560</v>
+        <v>366</v>
       </c>
       <c r="F261" s="2">
         <v>6</v>
@@ -6918,14 +6918,14 @@
       <c r="A262" s="1">
         <v>260</v>
       </c>
-      <c r="B262" s="2" t="s">
-        <v>157</v>
+      <c r="B262" s="1" t="s">
+        <v>535</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>368</v>
+        <v>174</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>561</v>
+        <v>367</v>
       </c>
       <c r="F262" s="2">
         <v>6</v>
@@ -6935,14 +6935,14 @@
       <c r="A263" s="1">
         <v>261</v>
       </c>
-      <c r="B263" s="2" t="s">
-        <v>157</v>
+      <c r="B263" s="1" t="s">
+        <v>535</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>562</v>
+        <v>368</v>
       </c>
       <c r="F263" s="2">
         <v>4</v>
@@ -6952,14 +6952,14 @@
       <c r="A264" s="1">
         <v>262</v>
       </c>
-      <c r="B264" s="2" t="s">
-        <v>157</v>
+      <c r="B264" s="1" t="s">
+        <v>535</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>368</v>
+        <v>174</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>563</v>
+        <v>369</v>
       </c>
       <c r="F264" s="2">
         <v>6</v>
@@ -6969,14 +6969,14 @@
       <c r="A265" s="1">
         <v>263</v>
       </c>
-      <c r="B265" s="2" t="s">
-        <v>158</v>
+      <c r="B265" s="1" t="s">
+        <v>536</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>369</v>
+        <v>175</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>564</v>
+        <v>370</v>
       </c>
       <c r="F265" s="2">
         <v>3</v>
@@ -6986,14 +6986,14 @@
       <c r="A266" s="1">
         <v>264</v>
       </c>
-      <c r="B266" s="2" t="s">
-        <v>159</v>
+      <c r="B266" s="1" t="s">
+        <v>537</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>311</v>
+        <v>117</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>565</v>
+        <v>371</v>
       </c>
       <c r="F266" s="2">
         <v>2</v>
@@ -7003,14 +7003,14 @@
       <c r="A267" s="1">
         <v>265</v>
       </c>
-      <c r="B267" s="2" t="s">
-        <v>160</v>
+      <c r="B267" s="1" t="s">
+        <v>538</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>302</v>
+        <v>108</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>482</v>
+        <v>288</v>
       </c>
       <c r="F267" s="2">
         <v>2</v>
@@ -7020,14 +7020,14 @@
       <c r="A268" s="1">
         <v>266</v>
       </c>
-      <c r="B268" s="2" t="s">
-        <v>161</v>
+      <c r="B268" s="1" t="s">
+        <v>539</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>260</v>
+        <v>66</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>549</v>
+        <v>355</v>
       </c>
       <c r="F268" s="2">
         <v>3</v>
@@ -7037,14 +7037,14 @@
       <c r="A269" s="1">
         <v>267</v>
       </c>
-      <c r="B269" s="2" t="s">
-        <v>161</v>
+      <c r="B269" s="1" t="s">
+        <v>539</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>260</v>
+        <v>66</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>449</v>
+        <v>255</v>
       </c>
       <c r="F269" s="2">
         <v>3</v>
@@ -7054,14 +7054,14 @@
       <c r="A270" s="1">
         <v>268</v>
       </c>
-      <c r="B270" s="2" t="s">
-        <v>162</v>
+      <c r="B270" s="1" t="s">
+        <v>540</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>370</v>
+        <v>176</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>475</v>
+        <v>281</v>
       </c>
       <c r="F270" s="2">
         <v>5</v>
@@ -7071,14 +7071,14 @@
       <c r="A271" s="1">
         <v>269</v>
       </c>
-      <c r="B271" s="2" t="s">
-        <v>162</v>
+      <c r="B271" s="1" t="s">
+        <v>540</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>288</v>
+        <v>94</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>566</v>
+        <v>372</v>
       </c>
       <c r="F271" s="2">
         <v>3</v>
@@ -7088,14 +7088,14 @@
       <c r="A272" s="1">
         <v>270</v>
       </c>
-      <c r="B272" s="2" t="s">
-        <v>163</v>
+      <c r="B272" s="1" t="s">
+        <v>541</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>371</v>
+        <v>177</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>486</v>
+        <v>292</v>
       </c>
       <c r="F272" s="2">
         <v>3</v>
@@ -7105,14 +7105,14 @@
       <c r="A273" s="1">
         <v>271</v>
       </c>
-      <c r="B273" s="2" t="s">
-        <v>163</v>
+      <c r="B273" s="1" t="s">
+        <v>541</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>371</v>
+        <v>177</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>503</v>
+        <v>309</v>
       </c>
       <c r="F273" s="2">
         <v>4</v>
@@ -7122,14 +7122,14 @@
       <c r="A274" s="1">
         <v>272</v>
       </c>
-      <c r="B274" s="2" t="s">
-        <v>164</v>
+      <c r="B274" s="1" t="s">
+        <v>542</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>232</v>
+        <v>38</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>417</v>
+        <v>223</v>
       </c>
       <c r="F274" s="2">
         <v>3</v>
@@ -7139,14 +7139,14 @@
       <c r="A275" s="1">
         <v>273</v>
       </c>
-      <c r="B275" s="2" t="s">
-        <v>165</v>
+      <c r="B275" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>338</v>
+        <v>144</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>511</v>
+        <v>317</v>
       </c>
       <c r="F275" s="2">
         <v>3</v>
@@ -7156,14 +7156,14 @@
       <c r="A276" s="1">
         <v>274</v>
       </c>
-      <c r="B276" s="2" t="s">
-        <v>165</v>
+      <c r="B276" s="1" t="s">
+        <v>543</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>372</v>
+        <v>178</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>555</v>
+        <v>361</v>
       </c>
       <c r="F276" s="2">
         <v>3</v>
@@ -7173,14 +7173,14 @@
       <c r="A277" s="1">
         <v>275</v>
       </c>
-      <c r="B277" s="2" t="s">
-        <v>166</v>
+      <c r="B277" s="1" t="s">
+        <v>544</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>270</v>
+        <v>76</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>440</v>
+        <v>246</v>
       </c>
       <c r="F277" s="2">
         <v>5</v>
@@ -7190,14 +7190,14 @@
       <c r="A278" s="1">
         <v>276</v>
       </c>
-      <c r="B278" s="2" t="s">
-        <v>167</v>
+      <c r="B278" s="1" t="s">
+        <v>545</v>
       </c>
       <c r="D278" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E278" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="F278" s="2">
         <v>7</v>
@@ -7207,14 +7207,14 @@
       <c r="A279" s="1">
         <v>277</v>
       </c>
-      <c r="B279" s="2" t="s">
-        <v>168</v>
+      <c r="B279" s="1" t="s">
+        <v>546</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>359</v>
+        <v>165</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>526</v>
+        <v>332</v>
       </c>
       <c r="F279" s="2">
         <v>3</v>
@@ -7224,14 +7224,14 @@
       <c r="A280" s="1">
         <v>278</v>
       </c>
-      <c r="B280" s="2" t="s">
-        <v>169</v>
+      <c r="B280" s="1" t="s">
+        <v>547</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>300</v>
+        <v>106</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>433</v>
+        <v>239</v>
       </c>
       <c r="F280" s="2">
         <v>3</v>
@@ -7241,14 +7241,14 @@
       <c r="A281" s="1">
         <v>279</v>
       </c>
-      <c r="B281" s="2" t="s">
-        <v>170</v>
+      <c r="B281" s="1" t="s">
+        <v>548</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>374</v>
+        <v>180</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>485</v>
+        <v>291</v>
       </c>
       <c r="F281" s="2">
         <v>3</v>
@@ -7258,14 +7258,14 @@
       <c r="A282" s="1">
         <v>280</v>
       </c>
-      <c r="B282" s="2" t="s">
-        <v>170</v>
+      <c r="B282" s="1" t="s">
+        <v>548</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>374</v>
+        <v>180</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>491</v>
+        <v>297</v>
       </c>
       <c r="F282" s="2">
         <v>3</v>
@@ -7275,14 +7275,14 @@
       <c r="A283" s="1">
         <v>281</v>
       </c>
-      <c r="B283" s="2" t="s">
-        <v>171</v>
+      <c r="B283" s="1" t="s">
+        <v>549</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>375</v>
+        <v>181</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>497</v>
+        <v>303</v>
       </c>
       <c r="F283" s="2">
         <v>2</v>
@@ -7292,14 +7292,14 @@
       <c r="A284" s="1">
         <v>282</v>
       </c>
-      <c r="B284" s="2" t="s">
-        <v>172</v>
+      <c r="B284" s="1" t="s">
+        <v>550</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>257</v>
+        <v>63</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>422</v>
+        <v>228</v>
       </c>
       <c r="F284" s="2">
         <v>3</v>
@@ -7309,14 +7309,14 @@
       <c r="A285" s="1">
         <v>283</v>
       </c>
-      <c r="B285" s="2" t="s">
-        <v>172</v>
+      <c r="B285" s="1" t="s">
+        <v>550</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>376</v>
+        <v>182</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>500</v>
+        <v>306</v>
       </c>
       <c r="F285" s="2">
         <v>4</v>
@@ -7326,14 +7326,14 @@
       <c r="A286" s="1">
         <v>284</v>
       </c>
-      <c r="B286" s="2" t="s">
-        <v>173</v>
+      <c r="B286" s="1" t="s">
+        <v>551</v>
       </c>
       <c r="D286" s="3" t="s">
-        <v>377</v>
+        <v>183</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>451</v>
+        <v>257</v>
       </c>
       <c r="F286" s="2">
         <v>3</v>
@@ -7343,14 +7343,14 @@
       <c r="A287" s="1">
         <v>285</v>
       </c>
-      <c r="B287" s="2" t="s">
-        <v>174</v>
+      <c r="B287" s="1" t="s">
+        <v>552</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>378</v>
+        <v>184</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>540</v>
+        <v>346</v>
       </c>
       <c r="F287" s="2">
         <v>4</v>
@@ -7360,14 +7360,14 @@
       <c r="A288" s="1">
         <v>286</v>
       </c>
-      <c r="B288" s="2" t="s">
-        <v>174</v>
+      <c r="B288" s="1" t="s">
+        <v>552</v>
       </c>
       <c r="D288" s="3" t="s">
-        <v>326</v>
+        <v>132</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>568</v>
+        <v>374</v>
       </c>
       <c r="F288" s="2">
         <v>1</v>
@@ -7377,14 +7377,14 @@
       <c r="A289" s="1">
         <v>287</v>
       </c>
-      <c r="B289" s="2" t="s">
-        <v>174</v>
+      <c r="B289" s="1" t="s">
+        <v>552</v>
       </c>
       <c r="D289" s="3" t="s">
-        <v>379</v>
+        <v>185</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>418</v>
+        <v>224</v>
       </c>
       <c r="F289" s="2">
         <v>2</v>
@@ -7394,14 +7394,14 @@
       <c r="A290" s="1">
         <v>288</v>
       </c>
-      <c r="B290" s="2" t="s">
-        <v>175</v>
+      <c r="B290" s="1" t="s">
+        <v>553</v>
       </c>
       <c r="D290" s="3" t="s">
-        <v>380</v>
+        <v>186</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>562</v>
+        <v>368</v>
       </c>
       <c r="F290" s="2">
         <v>4</v>
@@ -7411,14 +7411,14 @@
       <c r="A291" s="1">
         <v>289</v>
       </c>
-      <c r="B291" s="2" t="s">
-        <v>175</v>
+      <c r="B291" s="1" t="s">
+        <v>553</v>
       </c>
       <c r="D291" s="3" t="s">
-        <v>363</v>
+        <v>169</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>551</v>
+        <v>357</v>
       </c>
       <c r="F291" s="2">
         <v>3</v>
@@ -7428,14 +7428,14 @@
       <c r="A292" s="1">
         <v>290</v>
       </c>
-      <c r="B292" s="2" t="s">
-        <v>175</v>
+      <c r="B292" s="1" t="s">
+        <v>553</v>
       </c>
       <c r="D292" s="3" t="s">
-        <v>363</v>
+        <v>169</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>500</v>
+        <v>306</v>
       </c>
       <c r="F292" s="2">
         <v>3</v>
@@ -7445,14 +7445,14 @@
       <c r="A293" s="1">
         <v>291</v>
       </c>
-      <c r="B293" s="2" t="s">
-        <v>176</v>
+      <c r="B293" s="1" t="s">
+        <v>554</v>
       </c>
       <c r="D293" s="3" t="s">
-        <v>381</v>
+        <v>187</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>569</v>
+        <v>375</v>
       </c>
       <c r="F293" s="2">
         <v>5</v>
@@ -7462,14 +7462,14 @@
       <c r="A294" s="1">
         <v>292</v>
       </c>
-      <c r="B294" s="2" t="s">
-        <v>177</v>
+      <c r="B294" s="1" t="s">
+        <v>555</v>
       </c>
       <c r="D294" s="3" t="s">
-        <v>363</v>
+        <v>169</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>555</v>
+        <v>361</v>
       </c>
       <c r="F294" s="2">
         <v>3</v>
@@ -7479,14 +7479,14 @@
       <c r="A295" s="1">
         <v>293</v>
       </c>
-      <c r="B295" s="2" t="s">
-        <v>177</v>
+      <c r="B295" s="1" t="s">
+        <v>555</v>
       </c>
       <c r="D295" s="3" t="s">
-        <v>363</v>
+        <v>169</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>570</v>
+        <v>376</v>
       </c>
       <c r="F295" s="2">
         <v>4</v>
@@ -7496,14 +7496,14 @@
       <c r="A296" s="1">
         <v>294</v>
       </c>
-      <c r="B296" s="2" t="s">
-        <v>178</v>
+      <c r="B296" s="1" t="s">
+        <v>556</v>
       </c>
       <c r="D296" s="3" t="s">
-        <v>382</v>
+        <v>188</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>323</v>
+        <v>129</v>
       </c>
       <c r="F296" s="2">
         <v>3</v>
@@ -7513,14 +7513,14 @@
       <c r="A297" s="1">
         <v>295</v>
       </c>
-      <c r="B297" s="2" t="s">
-        <v>178</v>
+      <c r="B297" s="1" t="s">
+        <v>556</v>
       </c>
       <c r="D297" s="3" t="s">
-        <v>383</v>
+        <v>189</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>519</v>
+        <v>325</v>
       </c>
       <c r="F297" s="2">
         <v>3</v>
@@ -7530,14 +7530,14 @@
       <c r="A298" s="1">
         <v>296</v>
       </c>
-      <c r="B298" s="2" t="s">
-        <v>179</v>
+      <c r="B298" s="1" t="s">
+        <v>557</v>
       </c>
       <c r="D298" s="3" t="s">
-        <v>384</v>
+        <v>190</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>422</v>
+        <v>228</v>
       </c>
       <c r="F298" s="2">
         <v>4</v>
@@ -7547,14 +7547,14 @@
       <c r="A299" s="1">
         <v>297</v>
       </c>
-      <c r="B299" s="2" t="s">
-        <v>179</v>
+      <c r="B299" s="1" t="s">
+        <v>557</v>
       </c>
       <c r="D299" s="3" t="s">
-        <v>385</v>
+        <v>191</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>456</v>
+        <v>262</v>
       </c>
       <c r="F299" s="2">
         <v>5</v>
@@ -7564,14 +7564,14 @@
       <c r="A300" s="1">
         <v>298</v>
       </c>
-      <c r="B300" s="2" t="s">
-        <v>180</v>
+      <c r="B300" s="1" t="s">
+        <v>558</v>
       </c>
       <c r="D300" s="3" t="s">
-        <v>386</v>
+        <v>192</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>446</v>
+        <v>252</v>
       </c>
       <c r="F300" s="2">
         <v>5</v>
@@ -7581,14 +7581,14 @@
       <c r="A301" s="1">
         <v>299</v>
       </c>
-      <c r="B301" s="2" t="s">
-        <v>180</v>
+      <c r="B301" s="1" t="s">
+        <v>558</v>
       </c>
       <c r="D301" s="3" t="s">
-        <v>387</v>
+        <v>193</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>519</v>
+        <v>325</v>
       </c>
       <c r="F301" s="2">
         <v>1</v>
@@ -7598,14 +7598,14 @@
       <c r="A302" s="1">
         <v>300</v>
       </c>
-      <c r="B302" s="2" t="s">
-        <v>180</v>
+      <c r="B302" s="1" t="s">
+        <v>558</v>
       </c>
       <c r="D302" s="3" t="s">
-        <v>386</v>
+        <v>192</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>552</v>
+        <v>358</v>
       </c>
       <c r="F302" s="2">
         <v>5</v>
@@ -7615,14 +7615,14 @@
       <c r="A303" s="1">
         <v>301</v>
       </c>
-      <c r="B303" s="2" t="s">
-        <v>181</v>
+      <c r="B303" s="1" t="s">
+        <v>559</v>
       </c>
       <c r="D303" s="3" t="s">
-        <v>388</v>
+        <v>194</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>451</v>
+        <v>257</v>
       </c>
       <c r="F303" s="2">
         <v>4</v>
@@ -7632,14 +7632,14 @@
       <c r="A304" s="1">
         <v>302</v>
       </c>
-      <c r="B304" s="2" t="s">
-        <v>182</v>
+      <c r="B304" s="1" t="s">
+        <v>560</v>
       </c>
       <c r="D304" s="3" t="s">
-        <v>270</v>
+        <v>76</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>477</v>
+        <v>283</v>
       </c>
       <c r="F304" s="2">
         <v>5</v>
@@ -7649,14 +7649,14 @@
       <c r="A305" s="1">
         <v>303</v>
       </c>
-      <c r="B305" s="2" t="s">
-        <v>182</v>
+      <c r="B305" s="1" t="s">
+        <v>560</v>
       </c>
       <c r="D305" s="3" t="s">
-        <v>389</v>
+        <v>195</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>440</v>
+        <v>246</v>
       </c>
       <c r="F305" s="2">
         <v>7</v>
@@ -7666,14 +7666,14 @@
       <c r="A306" s="1">
         <v>304</v>
       </c>
-      <c r="B306" s="2" t="s">
-        <v>183</v>
+      <c r="B306" s="1" t="s">
+        <v>561</v>
       </c>
       <c r="D306" s="3" t="s">
-        <v>390</v>
+        <v>196</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>529</v>
+        <v>335</v>
       </c>
       <c r="F306" s="2">
         <v>7</v>
@@ -7683,14 +7683,14 @@
       <c r="A307" s="1">
         <v>305</v>
       </c>
-      <c r="B307" s="2" t="s">
-        <v>183</v>
+      <c r="B307" s="1" t="s">
+        <v>561</v>
       </c>
       <c r="D307" s="3" t="s">
-        <v>311</v>
+        <v>117</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>453</v>
+        <v>259</v>
       </c>
       <c r="F307" s="2">
         <v>2</v>
@@ -7700,14 +7700,14 @@
       <c r="A308" s="1">
         <v>306</v>
       </c>
-      <c r="B308" s="2" t="s">
-        <v>184</v>
+      <c r="B308" s="1" t="s">
+        <v>562</v>
       </c>
       <c r="D308" s="3" t="s">
-        <v>220</v>
+        <v>26</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>571</v>
+        <v>377</v>
       </c>
       <c r="F308" s="2">
         <v>3</v>
@@ -7717,14 +7717,14 @@
       <c r="A309" s="1">
         <v>307</v>
       </c>
-      <c r="B309" s="2" t="s">
-        <v>184</v>
+      <c r="B309" s="1" t="s">
+        <v>562</v>
       </c>
       <c r="D309" s="3" t="s">
-        <v>391</v>
+        <v>197</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>536</v>
+        <v>342</v>
       </c>
       <c r="F309" s="2">
         <v>4</v>
@@ -7734,14 +7734,14 @@
       <c r="A310" s="1">
         <v>308</v>
       </c>
-      <c r="B310" s="2" t="s">
-        <v>185</v>
+      <c r="B310" s="1" t="s">
+        <v>563</v>
       </c>
       <c r="D310" s="3" t="s">
-        <v>358</v>
+        <v>164</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>572</v>
+        <v>378</v>
       </c>
       <c r="F310" s="2">
         <v>2</v>
@@ -7751,14 +7751,14 @@
       <c r="A311" s="1">
         <v>309</v>
       </c>
-      <c r="B311" s="2" t="s">
-        <v>185</v>
+      <c r="B311" s="1" t="s">
+        <v>563</v>
       </c>
       <c r="D311" s="3" t="s">
-        <v>358</v>
+        <v>164</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>423</v>
+        <v>229</v>
       </c>
       <c r="F311" s="2">
         <v>3</v>
@@ -7768,14 +7768,14 @@
       <c r="A312" s="1">
         <v>310</v>
       </c>
-      <c r="B312" s="2" t="s">
-        <v>186</v>
+      <c r="B312" s="1" t="s">
+        <v>564</v>
       </c>
       <c r="D312" s="3" t="s">
-        <v>311</v>
+        <v>117</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>573</v>
+        <v>379</v>
       </c>
       <c r="F312" s="2">
         <v>2</v>
@@ -7785,14 +7785,14 @@
       <c r="A313" s="1">
         <v>311</v>
       </c>
-      <c r="B313" s="2" t="s">
-        <v>186</v>
+      <c r="B313" s="1" t="s">
+        <v>564</v>
       </c>
       <c r="D313" s="3" t="s">
-        <v>311</v>
+        <v>117</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>429</v>
+        <v>235</v>
       </c>
       <c r="F313" s="2">
         <v>2</v>
@@ -7802,14 +7802,14 @@
       <c r="A314" s="1">
         <v>312</v>
       </c>
-      <c r="B314" s="2" t="s">
-        <v>187</v>
+      <c r="B314" s="1" t="s">
+        <v>565</v>
       </c>
       <c r="D314" s="3" t="s">
-        <v>392</v>
+        <v>198</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>502</v>
+        <v>308</v>
       </c>
       <c r="F314" s="2">
         <v>2</v>
@@ -7819,14 +7819,14 @@
       <c r="A315" s="1">
         <v>313</v>
       </c>
-      <c r="B315" s="2" t="s">
-        <v>187</v>
+      <c r="B315" s="1" t="s">
+        <v>565</v>
       </c>
       <c r="D315" s="3" t="s">
-        <v>391</v>
+        <v>197</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>488</v>
+        <v>294</v>
       </c>
       <c r="F315" s="2">
         <v>3</v>
@@ -7836,14 +7836,14 @@
       <c r="A316" s="1">
         <v>314</v>
       </c>
-      <c r="B316" s="2" t="s">
-        <v>187</v>
+      <c r="B316" s="1" t="s">
+        <v>565</v>
       </c>
       <c r="D316" s="3" t="s">
-        <v>392</v>
+        <v>198</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>457</v>
+        <v>263</v>
       </c>
       <c r="F316" s="2">
         <v>3</v>
@@ -7853,14 +7853,14 @@
       <c r="A317" s="1">
         <v>315</v>
       </c>
-      <c r="B317" s="2" t="s">
-        <v>187</v>
+      <c r="B317" s="1" t="s">
+        <v>565</v>
       </c>
       <c r="D317" s="3" t="s">
-        <v>392</v>
+        <v>198</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>552</v>
+        <v>358</v>
       </c>
       <c r="F317" s="2">
         <v>3</v>
@@ -7870,14 +7870,14 @@
       <c r="A318" s="1">
         <v>316</v>
       </c>
-      <c r="B318" s="2" t="s">
-        <v>188</v>
+      <c r="B318" s="1" t="s">
+        <v>566</v>
       </c>
       <c r="D318" s="3" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>540</v>
+        <v>346</v>
       </c>
       <c r="F318" s="2">
         <v>3</v>
@@ -7887,14 +7887,14 @@
       <c r="A319" s="1">
         <v>317</v>
       </c>
-      <c r="B319" s="2" t="s">
-        <v>188</v>
+      <c r="B319" s="1" t="s">
+        <v>566</v>
       </c>
       <c r="D319" s="3" t="s">
-        <v>222</v>
+        <v>28</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>457</v>
+        <v>263</v>
       </c>
       <c r="F319" s="2">
         <v>4</v>
@@ -7904,14 +7904,14 @@
       <c r="A320" s="1">
         <v>318</v>
       </c>
-      <c r="B320" s="2" t="s">
-        <v>189</v>
+      <c r="B320" s="1" t="s">
+        <v>567</v>
       </c>
       <c r="D320" s="3" t="s">
-        <v>393</v>
+        <v>199</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>574</v>
+        <v>380</v>
       </c>
       <c r="F320" s="2">
         <v>4</v>
@@ -7921,14 +7921,14 @@
       <c r="A321" s="1">
         <v>319</v>
       </c>
-      <c r="B321" s="2" t="s">
-        <v>190</v>
+      <c r="B321" s="1" t="s">
+        <v>568</v>
       </c>
       <c r="D321" s="3" t="s">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>500</v>
+        <v>306</v>
       </c>
       <c r="F321" s="2">
         <v>4</v>
@@ -7938,14 +7938,14 @@
       <c r="A322" s="1">
         <v>320</v>
       </c>
-      <c r="B322" s="2" t="s">
-        <v>191</v>
+      <c r="B322" s="1" t="s">
+        <v>569</v>
       </c>
       <c r="D322" s="3" t="s">
-        <v>394</v>
+        <v>200</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>451</v>
+        <v>257</v>
       </c>
       <c r="F322" s="2">
         <v>1</v>
@@ -7955,14 +7955,14 @@
       <c r="A323" s="1">
         <v>321</v>
       </c>
-      <c r="B323" s="2" t="s">
-        <v>192</v>
+      <c r="B323" s="1" t="s">
+        <v>570</v>
       </c>
       <c r="D323" s="3" t="s">
-        <v>395</v>
+        <v>201</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>575</v>
+        <v>381</v>
       </c>
       <c r="F323" s="2">
         <v>2</v>
@@ -7972,14 +7972,14 @@
       <c r="A324" s="1">
         <v>322</v>
       </c>
-      <c r="B324" s="2" t="s">
-        <v>192</v>
+      <c r="B324" s="1" t="s">
+        <v>570</v>
       </c>
       <c r="D324" s="3" t="s">
-        <v>248</v>
+        <v>54</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>576</v>
+        <v>382</v>
       </c>
       <c r="F324" s="2">
         <v>2</v>
@@ -7989,14 +7989,14 @@
       <c r="A325" s="1">
         <v>323</v>
       </c>
-      <c r="B325" s="2" t="s">
-        <v>193</v>
+      <c r="B325" s="1" t="s">
+        <v>571</v>
       </c>
       <c r="D325" s="3" t="s">
-        <v>290</v>
+        <v>96</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>454</v>
+        <v>260</v>
       </c>
       <c r="F325" s="2">
         <v>2</v>
@@ -8006,14 +8006,14 @@
       <c r="A326" s="1">
         <v>324</v>
       </c>
-      <c r="B326" s="2" t="s">
-        <v>194</v>
+      <c r="B326" s="1" t="s">
+        <v>572</v>
       </c>
       <c r="D326" s="3" t="s">
-        <v>263</v>
+        <v>69</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>577</v>
+        <v>383</v>
       </c>
       <c r="F326" s="2">
         <v>1</v>
@@ -8023,14 +8023,14 @@
       <c r="A327" s="1">
         <v>325</v>
       </c>
-      <c r="B327" s="2" t="s">
-        <v>194</v>
+      <c r="B327" s="1" t="s">
+        <v>572</v>
       </c>
       <c r="D327" s="3" t="s">
-        <v>396</v>
+        <v>202</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>424</v>
+        <v>230</v>
       </c>
       <c r="F327" s="2">
         <v>3</v>
@@ -8040,14 +8040,14 @@
       <c r="A328" s="1">
         <v>326</v>
       </c>
-      <c r="B328" s="2" t="s">
-        <v>195</v>
+      <c r="B328" s="1" t="s">
+        <v>573</v>
       </c>
       <c r="D328" s="3" t="s">
-        <v>350</v>
+        <v>156</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>578</v>
+        <v>384</v>
       </c>
       <c r="F328" s="2">
         <v>3</v>
@@ -8057,14 +8057,14 @@
       <c r="A329" s="1">
         <v>327</v>
       </c>
-      <c r="B329" s="2" t="s">
-        <v>196</v>
+      <c r="B329" s="1" t="s">
+        <v>574</v>
       </c>
       <c r="D329" s="3" t="s">
-        <v>279</v>
+        <v>85</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>579</v>
+        <v>385</v>
       </c>
       <c r="F329" s="2">
         <v>3</v>
@@ -8074,14 +8074,14 @@
       <c r="A330" s="1">
         <v>328</v>
       </c>
-      <c r="B330" s="2" t="s">
-        <v>196</v>
+      <c r="B330" s="1" t="s">
+        <v>574</v>
       </c>
       <c r="D330" s="3" t="s">
-        <v>279</v>
+        <v>85</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>476</v>
+        <v>282</v>
       </c>
       <c r="F330" s="2">
         <v>3</v>
@@ -8091,14 +8091,14 @@
       <c r="A331" s="1">
         <v>329</v>
       </c>
-      <c r="B331" s="2" t="s">
-        <v>197</v>
+      <c r="B331" s="1" t="s">
+        <v>575</v>
       </c>
       <c r="D331" s="3" t="s">
-        <v>397</v>
+        <v>203</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>529</v>
+        <v>335</v>
       </c>
       <c r="F331" s="2">
         <v>5</v>
@@ -8108,14 +8108,14 @@
       <c r="A332" s="1">
         <v>330</v>
       </c>
-      <c r="B332" s="2" t="s">
-        <v>197</v>
+      <c r="B332" s="1" t="s">
+        <v>575</v>
       </c>
       <c r="D332" s="3" t="s">
-        <v>287</v>
+        <v>93</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>530</v>
+        <v>336</v>
       </c>
       <c r="F332" s="2">
         <v>2</v>
@@ -8125,14 +8125,14 @@
       <c r="A333" s="1">
         <v>331</v>
       </c>
-      <c r="B333" s="2" t="s">
-        <v>197</v>
+      <c r="B333" s="1" t="s">
+        <v>575</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>287</v>
+        <v>93</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>436</v>
+        <v>242</v>
       </c>
       <c r="F333" s="2">
         <v>2</v>
@@ -8142,14 +8142,14 @@
       <c r="A334" s="1">
         <v>332</v>
       </c>
-      <c r="B334" s="2" t="s">
-        <v>197</v>
+      <c r="B334" s="1" t="s">
+        <v>575</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>398</v>
+        <v>204</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>414</v>
+        <v>220</v>
       </c>
       <c r="F334" s="2">
         <v>3</v>
@@ -8159,14 +8159,14 @@
       <c r="A335" s="1">
         <v>333</v>
       </c>
-      <c r="B335" s="2" t="s">
-        <v>198</v>
+      <c r="B335" s="1" t="s">
+        <v>576</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>271</v>
+        <v>77</v>
       </c>
       <c r="E335" s="2" t="s">
-        <v>454</v>
+        <v>260</v>
       </c>
       <c r="F335" s="2">
         <v>4</v>
@@ -8176,14 +8176,14 @@
       <c r="A336" s="1">
         <v>334</v>
       </c>
-      <c r="B336" s="2" t="s">
-        <v>198</v>
+      <c r="B336" s="1" t="s">
+        <v>576</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>399</v>
+        <v>205</v>
       </c>
       <c r="E336" s="2" t="s">
-        <v>566</v>
+        <v>372</v>
       </c>
       <c r="F336" s="2">
         <v>1</v>
@@ -8193,14 +8193,14 @@
       <c r="A337" s="1">
         <v>335</v>
       </c>
-      <c r="B337" s="2" t="s">
-        <v>199</v>
+      <c r="B337" s="1" t="s">
+        <v>577</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>400</v>
+        <v>206</v>
       </c>
       <c r="E337" s="2" t="s">
-        <v>509</v>
+        <v>315</v>
       </c>
       <c r="F337" s="2">
         <v>3</v>
@@ -8210,14 +8210,14 @@
       <c r="A338" s="1">
         <v>336</v>
       </c>
-      <c r="B338" s="2" t="s">
-        <v>199</v>
+      <c r="B338" s="1" t="s">
+        <v>577</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>400</v>
+        <v>206</v>
       </c>
       <c r="E338" s="2" t="s">
-        <v>580</v>
+        <v>386</v>
       </c>
       <c r="F338" s="2">
         <v>3</v>
@@ -8227,14 +8227,14 @@
       <c r="A339" s="1">
         <v>337</v>
       </c>
-      <c r="B339" s="2" t="s">
-        <v>200</v>
+      <c r="B339" s="1" t="s">
+        <v>578</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>401</v>
+        <v>207</v>
       </c>
       <c r="E339" s="2" t="s">
-        <v>581</v>
+        <v>387</v>
       </c>
       <c r="F339" s="2">
         <v>5</v>
@@ -8244,14 +8244,14 @@
       <c r="A340" s="1">
         <v>338</v>
       </c>
-      <c r="B340" s="2" t="s">
-        <v>201</v>
+      <c r="B340" s="1" t="s">
+        <v>579</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>402</v>
+        <v>208</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>486</v>
+        <v>292</v>
       </c>
       <c r="F340" s="2">
         <v>3</v>
@@ -8261,14 +8261,14 @@
       <c r="A341" s="1">
         <v>339</v>
       </c>
-      <c r="B341" s="2" t="s">
-        <v>201</v>
+      <c r="B341" s="1" t="s">
+        <v>579</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>403</v>
+        <v>209</v>
       </c>
       <c r="E341" s="2" t="s">
-        <v>578</v>
+        <v>384</v>
       </c>
       <c r="F341" s="2">
         <v>4</v>
@@ -8278,14 +8278,14 @@
       <c r="A342" s="1">
         <v>340</v>
       </c>
-      <c r="B342" s="2" t="s">
-        <v>201</v>
+      <c r="B342" s="1" t="s">
+        <v>579</v>
       </c>
       <c r="D342" s="3" t="s">
-        <v>403</v>
+        <v>209</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>582</v>
+        <v>388</v>
       </c>
       <c r="F342" s="2">
         <v>4</v>
@@ -8295,14 +8295,14 @@
       <c r="A343" s="1">
         <v>341</v>
       </c>
-      <c r="B343" s="2" t="s">
-        <v>202</v>
+      <c r="B343" s="1" t="s">
+        <v>580</v>
       </c>
       <c r="D343" s="3" t="s">
-        <v>404</v>
+        <v>210</v>
       </c>
       <c r="E343" s="2" t="s">
-        <v>534</v>
+        <v>340</v>
       </c>
       <c r="F343" s="2">
         <v>2</v>
@@ -8312,14 +8312,14 @@
       <c r="A344" s="1">
         <v>342</v>
       </c>
-      <c r="B344" s="2" t="s">
-        <v>203</v>
+      <c r="B344" s="1" t="s">
+        <v>581</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>405</v>
+        <v>211</v>
       </c>
       <c r="E344" s="2" t="s">
-        <v>583</v>
+        <v>389</v>
       </c>
       <c r="F344" s="2">
         <v>2</v>
@@ -8329,14 +8329,14 @@
       <c r="A345" s="1">
         <v>343</v>
       </c>
-      <c r="B345" s="2" t="s">
-        <v>204</v>
+      <c r="B345" s="1" t="s">
+        <v>582</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>396</v>
+        <v>202</v>
       </c>
       <c r="E345" s="2" t="s">
-        <v>484</v>
+        <v>290</v>
       </c>
       <c r="F345" s="2">
         <v>3</v>
@@ -8346,14 +8346,14 @@
       <c r="A346" s="1">
         <v>344</v>
       </c>
-      <c r="B346" s="2" t="s">
-        <v>204</v>
+      <c r="B346" s="1" t="s">
+        <v>582</v>
       </c>
       <c r="D346" s="3" t="s">
-        <v>396</v>
+        <v>202</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>584</v>
+        <v>390</v>
       </c>
       <c r="F346" s="2">
         <v>4</v>
@@ -8363,14 +8363,14 @@
       <c r="A347" s="1">
         <v>345</v>
       </c>
-      <c r="B347" s="2" t="s">
-        <v>205</v>
+      <c r="B347" s="1" t="s">
+        <v>583</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>406</v>
+        <v>212</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>423</v>
+        <v>229</v>
       </c>
       <c r="F347" s="2">
         <v>2</v>
@@ -8380,14 +8380,14 @@
       <c r="A348" s="1">
         <v>346</v>
       </c>
-      <c r="B348" s="2" t="s">
-        <v>206</v>
+      <c r="B348" s="1" t="s">
+        <v>584</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>369</v>
+        <v>175</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>537</v>
+        <v>343</v>
       </c>
       <c r="F348" s="2">
         <v>2</v>
@@ -8397,14 +8397,14 @@
       <c r="A349" s="1">
         <v>347</v>
       </c>
-      <c r="B349" s="2" t="s">
-        <v>207</v>
+      <c r="B349" s="1" t="s">
+        <v>585</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>273</v>
+        <v>79</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>484</v>
+        <v>290</v>
       </c>
       <c r="F349" s="2">
         <v>4</v>
@@ -8414,14 +8414,14 @@
       <c r="A350" s="1">
         <v>348</v>
       </c>
-      <c r="B350" s="2" t="s">
-        <v>208</v>
+      <c r="B350" s="1" t="s">
+        <v>586</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>256</v>
+        <v>62</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>449</v>
+        <v>255</v>
       </c>
       <c r="F350" s="2">
         <v>3</v>
@@ -8431,14 +8431,14 @@
       <c r="A351" s="1">
         <v>349</v>
       </c>
-      <c r="B351" s="2" t="s">
-        <v>208</v>
+      <c r="B351" s="1" t="s">
+        <v>586</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>256</v>
+        <v>62</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>585</v>
+        <v>391</v>
       </c>
       <c r="F351" s="2">
         <v>3</v>
@@ -8448,14 +8448,14 @@
       <c r="A352" s="1">
         <v>350</v>
       </c>
-      <c r="B352" s="2" t="s">
-        <v>208</v>
+      <c r="B352" s="1" t="s">
+        <v>586</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>256</v>
+        <v>62</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>478</v>
+        <v>284</v>
       </c>
       <c r="F352" s="2">
         <v>4</v>
@@ -8465,14 +8465,14 @@
       <c r="A353" s="1">
         <v>351</v>
       </c>
-      <c r="B353" s="2" t="s">
-        <v>208</v>
+      <c r="B353" s="1" t="s">
+        <v>586</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>407</v>
+        <v>213</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>586</v>
+        <v>392</v>
       </c>
       <c r="F353" s="2">
         <v>1</v>
@@ -8482,14 +8482,14 @@
       <c r="A354" s="1">
         <v>352</v>
       </c>
-      <c r="B354" s="2" t="s">
-        <v>209</v>
+      <c r="B354" s="1" t="s">
+        <v>587</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>236</v>
+        <v>42</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>587</v>
+        <v>393</v>
       </c>
       <c r="F354" s="2">
         <v>2</v>
@@ -8499,14 +8499,14 @@
       <c r="A355" s="1">
         <v>353</v>
       </c>
-      <c r="B355" s="2" t="s">
-        <v>209</v>
+      <c r="B355" s="1" t="s">
+        <v>587</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>227</v>
+        <v>33</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>486</v>
+        <v>292</v>
       </c>
       <c r="F355" s="2">
         <v>3</v>
@@ -8516,14 +8516,14 @@
       <c r="A356" s="1">
         <v>354</v>
       </c>
-      <c r="B356" s="2" t="s">
-        <v>209</v>
+      <c r="B356" s="1" t="s">
+        <v>587</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>408</v>
+        <v>214</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>572</v>
+        <v>378</v>
       </c>
       <c r="F356" s="2">
         <v>3</v>
@@ -8533,14 +8533,14 @@
       <c r="A357" s="1">
         <v>355</v>
       </c>
-      <c r="B357" s="2" t="s">
-        <v>210</v>
+      <c r="B357" s="1" t="s">
+        <v>588</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>322</v>
+        <v>128</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>501</v>
+        <v>307</v>
       </c>
       <c r="F357" s="2">
         <v>4</v>
@@ -8550,14 +8550,14 @@
       <c r="A358" s="1">
         <v>356</v>
       </c>
-      <c r="B358" s="2" t="s">
-        <v>210</v>
+      <c r="B358" s="1" t="s">
+        <v>588</v>
       </c>
       <c r="D358" s="3" t="s">
-        <v>322</v>
+        <v>128</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>519</v>
+        <v>325</v>
       </c>
       <c r="F358" s="2">
         <v>5</v>
@@ -8567,14 +8567,14 @@
       <c r="A359" s="1">
         <v>357</v>
       </c>
-      <c r="B359" s="2" t="s">
-        <v>210</v>
+      <c r="B359" s="1" t="s">
+        <v>588</v>
       </c>
       <c r="D359" s="3" t="s">
-        <v>279</v>
+        <v>85</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>588</v>
+        <v>394</v>
       </c>
       <c r="F359" s="2">
         <v>3</v>
@@ -8584,14 +8584,14 @@
       <c r="A360" s="1">
         <v>358</v>
       </c>
-      <c r="B360" s="2" t="s">
-        <v>211</v>
+      <c r="B360" s="1" t="s">
+        <v>589</v>
       </c>
       <c r="D360" s="3" t="s">
-        <v>320</v>
+        <v>126</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>470</v>
+        <v>276</v>
       </c>
       <c r="F360" s="2">
         <v>2</v>
@@ -8601,14 +8601,14 @@
       <c r="A361" s="1">
         <v>359</v>
       </c>
-      <c r="B361" s="2" t="s">
-        <v>211</v>
+      <c r="B361" s="1" t="s">
+        <v>589</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>320</v>
+        <v>126</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>589</v>
+        <v>395</v>
       </c>
       <c r="F361" s="2">
         <v>3</v>
@@ -8618,14 +8618,14 @@
       <c r="A362" s="1">
         <v>360</v>
       </c>
-      <c r="B362" s="2" t="s">
-        <v>212</v>
+      <c r="B362" s="1" t="s">
+        <v>590</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>409</v>
+        <v>215</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>590</v>
+        <v>396</v>
       </c>
       <c r="F362" s="2">
         <v>5</v>
@@ -8635,14 +8635,14 @@
       <c r="A363" s="1">
         <v>361</v>
       </c>
-      <c r="B363" s="2" t="s">
-        <v>213</v>
+      <c r="B363" s="1" t="s">
+        <v>591</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>410</v>
+        <v>216</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>591</v>
+        <v>397</v>
       </c>
       <c r="F363" s="2">
         <v>2</v>
@@ -8654,11 +8654,11 @@
     <mergeCell ref="L1:P1"/>
     <mergeCell ref="Q1:V1"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
+    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8829,13 +8829,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C740B79-F876-4FFC-9AA8-02E54C2AC858}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18F5E774-32FD-466E-A395-17935A3755AA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E4E4BF0-3005-46D3-8F96-7D0B30121ACE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{764B0CFB-49D4-4830-9107-49EA10D9B613}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD00E43C-EE53-4D16-A494-A479C2097C1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{06BC6F86-7933-4DFC-979B-4E394D5D8C04}"/>
 </file>